--- a/app/doc/PDA VIEW SQL_20251031.xlsx
+++ b/app/doc/PDA VIEW SQL_20251031.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PDA\PDA-INNO\app\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA1783E-57E7-4684-BFE1-5E27386C9F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A90709F-359D-49BD-A443-7FC69DA22C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VW_PDA_WID_LIST" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4233" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="1085">
   <si>
     <t>COLUMN_NAME</t>
   </si>
@@ -2420,9 +2420,6 @@
     <t>이마트 창고코드</t>
   </si>
   <si>
-    <t>REF_CODE2</t>
-  </si>
-  <si>
     <t>MASTER_CODE=HOMEPLUS_ORIGIN_CODE</t>
   </si>
   <si>
@@ -2439,9 +2436,6 @@
   </si>
   <si>
     <t>MASTER_CODE=EMART_SCALE_BARCODE_USE_CENTER</t>
-  </si>
-  <si>
-    <t>CENTER_SCALE_USE_YN</t>
   </si>
   <si>
     <t>센터 계근 바코드 사용여부</t>
@@ -3218,10 +3212,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>수주수쟝KG</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>수주금액</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -3515,6 +3505,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -3646,6 +3637,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>, J:</t>
@@ -3665,6 +3657,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>, B:</t>
@@ -3683,10 +3676,6 @@
   </si>
   <si>
     <t>품목코드.낱개중량</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>왜 필요한지</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -4025,6 +4014,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4044,6 +4034,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4063,6 +4054,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> - </t>
@@ -4082,6 +4074,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 6</t>
@@ -4101,6 +4094,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4120,6 +4114,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -4140,6 +4135,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4159,6 +4155,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> - </t>
@@ -4178,6 +4175,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4197,6 +4195,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(W_GOODS_WET)</t>
@@ -4216,6 +4215,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4235,6 +4235,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4270,6 +4271,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4289,6 +4291,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> - </t>
@@ -4308,6 +4311,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4327,6 +4331,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -4347,6 +4352,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4366,6 +4372,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> - </t>
@@ -4385,6 +4392,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4404,6 +4412,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(W_GOODS_WET)</t>
@@ -4423,6 +4432,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4442,6 +4452,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4478,6 +4489,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4497,6 +4509,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4516,6 +4529,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -4636,6 +4650,294 @@
   </si>
   <si>
     <t>PACKING_QTY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOODS_R_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                     ON ID.GOODS_R_ID = WR.GOODS_R_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMPORT_ID_NO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GI_H_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BL_NO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_SPEC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BL_D_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BL_S_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GR_WAREHOUSE_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONTRACT_TYPE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PACKER_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PACKER_PRODUCT_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFER_D_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_TYPE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>STORE_NAME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CENTER_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NAME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PACKWEIGHT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMARTLOGIS_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMARTITEM_CODE와 다른점</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X (C0117 매출처품목코드)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">X  (C0117 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매출처품목코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">X (C0705 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>품목코드관리)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>USE_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CENTERNAME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WH_AREA</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CT_NAME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>USE_NAME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CENTER_SCALE_USE_YN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRANDNAME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BARCODEGOODS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMART_PLANT_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">O  (C0117 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매출처품목코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GI_D_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EOI_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMARTITEM_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMARTITEM</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GI_REQ_PKG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GI_REQ_QTY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GR_REF_NO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GI_REQ_DATE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRAND_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLIENT_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MASTER_CODE=EMART_STORE_CODE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                     INNER JOIN B_COMMON_CODE BCC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>REF_CODE2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>W_GOODS_IH (IH) - 출고 헤더 -&gt; SM_출고머리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>W_GOODS_ID (ID) - 출고 상세 -&gt; SM_출고상세</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>출고수량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>출고중량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">          "WH_AREA",</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4661,6 +4963,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4986,19 +5289,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5014,9 +5304,22 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -5233,14 +5536,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1013"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:K192"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="53.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="29" style="6" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" style="6" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="32" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="38.28515625" style="6" customWidth="1"/>
     <col min="8" max="8" width="27.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.140625" style="6" bestFit="1" customWidth="1"/>
@@ -5250,18 +5553,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5">
-      <c r="A1" s="30" t="s">
-        <v>884</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="32"/>
+      <c r="A1" s="37" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39"/>
       <c r="K1" s="9"/>
     </row>
     <row r="2" spans="1:11" ht="16.5">
@@ -5278,13 +5581,13 @@
         <v>4</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>708</v>
@@ -5296,12 +5599,12 @@
         <v>710</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5">
       <c r="A3" s="20" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>9</v>
@@ -5312,14 +5615,14 @@
       <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="37" t="s">
-        <v>1023</v>
+      <c r="E3" s="30" t="s">
+        <v>1018</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>8</v>
@@ -5333,7 +5636,7 @@
     </row>
     <row r="4" spans="1:11" ht="33">
       <c r="A4" s="20" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>19</v>
@@ -5344,14 +5647,14 @@
       <c r="D4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>1023</v>
+      <c r="E4" s="30" t="s">
+        <v>1019</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>49</v>
@@ -5365,7 +5668,7 @@
     </row>
     <row r="5" spans="1:11" ht="16.5">
       <c r="A5" s="20" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>40</v>
@@ -5376,11 +5679,11 @@
       <c r="D5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>1022</v>
+      <c r="E5" s="30" t="s">
+        <v>1018</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
@@ -5393,20 +5696,19 @@
         <v>716</v>
       </c>
     </row>
-    <row r="6" spans="1:11"/>
     <row r="7" spans="1:11" ht="16.5">
-      <c r="A7" s="30" t="s">
-        <v>885</v>
-      </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
+      <c r="A7" s="37" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="7" t="s">
@@ -5423,10 +5725,10 @@
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>708</v>
@@ -5439,8 +5741,8 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.5">
-      <c r="A9" s="8" t="s">
-        <v>8</v>
+      <c r="A9" s="20" t="s">
+        <v>1032</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>9</v>
@@ -5451,11 +5753,11 @@
       <c r="D9" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E9" s="37" t="s">
-        <v>1023</v>
+      <c r="E9" s="30" t="s">
+        <v>1018</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8" t="s">
@@ -5470,7 +5772,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="20" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>9</v>
@@ -5481,11 +5783,11 @@
       <c r="D10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>1022</v>
+      <c r="E10" s="30" t="s">
+        <v>1018</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8" t="s">
@@ -5500,7 +5802,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5">
       <c r="A11" s="20" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>16</v>
@@ -5511,12 +5813,12 @@
       <c r="D11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="37" t="s">
-        <v>1023</v>
+      <c r="E11" s="30" t="s">
+        <v>1018</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="22" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>15</v>
@@ -5530,10 +5832,10 @@
     </row>
     <row r="12" spans="1:11" ht="16.5">
       <c r="A12" s="20" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>10</v>
@@ -5541,11 +5843,11 @@
       <c r="D12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="37" t="s">
-        <v>1022</v>
+      <c r="E12" s="30" t="s">
+        <v>1018</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
@@ -5560,7 +5862,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5">
       <c r="A13" s="20" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>9</v>
@@ -5571,9 +5873,11 @@
       <c r="D13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="38"/>
+      <c r="E13" s="30" t="s">
+        <v>1027</v>
+      </c>
       <c r="F13" s="21" t="s">
-        <v>889</v>
+        <v>1082</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8" t="s">
@@ -5588,7 +5892,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5">
       <c r="A14" s="20" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>9</v>
@@ -5599,9 +5903,11 @@
       <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="38"/>
+      <c r="E14" s="30" t="s">
+        <v>1027</v>
+      </c>
       <c r="F14" s="21" t="s">
-        <v>890</v>
+        <v>1083</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8" t="s">
@@ -5616,7 +5922,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5">
       <c r="A15" s="20" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>9</v>
@@ -5627,10 +5933,10 @@
       <c r="D15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="21" t="s">
-        <v>891</v>
-      </c>
+      <c r="E15" s="30" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F15" s="21"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -5643,8 +5949,8 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="8" t="s">
-        <v>1028</v>
+      <c r="A16" s="20" t="s">
+        <v>1024</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>9</v>
@@ -5655,9 +5961,11 @@
       <c r="D16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="38"/>
+      <c r="E16" s="30" t="s">
+        <v>1027</v>
+      </c>
       <c r="F16" s="20" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8" t="s">
@@ -5672,7 +5980,7 @@
     </row>
     <row r="17" spans="1:10" ht="16.5">
       <c r="A17" s="20" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>45</v>
@@ -5683,9 +5991,11 @@
       <c r="D17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="38"/>
+      <c r="E17" s="30" t="s">
+        <v>1027</v>
+      </c>
       <c r="F17" s="20" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8" t="s">
@@ -5700,7 +6010,7 @@
     </row>
     <row r="18" spans="1:10" ht="16.5">
       <c r="A18" s="20" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>9</v>
@@ -5711,10 +6021,12 @@
       <c r="D18" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E18" s="38"/>
+      <c r="E18" s="30" t="s">
+        <v>1027</v>
+      </c>
       <c r="F18" s="8"/>
       <c r="G18" s="21" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>717</v>
@@ -5726,20 +6038,19 @@
         <v>737</v>
       </c>
     </row>
-    <row r="19" spans="1:10"/>
     <row r="20" spans="1:10" ht="16.5">
-      <c r="A20" s="30" t="s">
-        <v>893</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="32"/>
+      <c r="A20" s="37" t="s">
+        <v>890</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="7" t="s">
@@ -5756,7 +6067,7 @@
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7" t="s">
@@ -5782,9 +6093,11 @@
       <c r="D22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="38"/>
+      <c r="E22" s="30" t="s">
+        <v>1027</v>
+      </c>
       <c r="F22" s="20" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8" t="s">
@@ -5799,7 +6112,7 @@
     </row>
     <row r="23" spans="1:10" ht="16.5">
       <c r="A23" s="20" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>19</v>
@@ -5810,9 +6123,11 @@
       <c r="D23" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="38"/>
+      <c r="E23" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F23" s="21" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8" t="s">
@@ -5826,8 +6141,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.5">
-      <c r="A24" s="8" t="s">
-        <v>64</v>
+      <c r="A24" s="20" t="s">
+        <v>1031</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>27</v>
@@ -5838,9 +6153,11 @@
       <c r="D24" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="38"/>
+      <c r="E24" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F24" s="21" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8" t="s">
@@ -5854,8 +6171,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.5">
-      <c r="A25" s="8" t="s">
-        <v>42</v>
+      <c r="A25" s="20" t="s">
+        <v>1033</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>27</v>
@@ -5866,10 +6183,12 @@
       <c r="D25" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="E25" s="38"/>
+      <c r="E25" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F25" s="8"/>
       <c r="G25" s="21" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>42</v>
@@ -5882,8 +6201,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="33">
-      <c r="A26" s="8" t="s">
-        <v>56</v>
+      <c r="A26" s="20" t="s">
+        <v>1034</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>57</v>
@@ -5894,10 +6213,12 @@
       <c r="D26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="38"/>
+      <c r="E26" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F26" s="8"/>
       <c r="G26" s="21" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>56</v>
@@ -5922,12 +6243,14 @@
       <c r="D27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E27" s="38"/>
+      <c r="E27" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F27" s="21" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>59</v>
@@ -5940,8 +6263,8 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="8" t="s">
-        <v>751</v>
+      <c r="A28" s="20" t="s">
+        <v>1036</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>9</v>
@@ -5952,9 +6275,11 @@
       <c r="D28" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E28" s="38"/>
+      <c r="E28" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F28" s="20" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8" t="s">
@@ -5968,8 +6293,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.5">
-      <c r="A29" s="8" t="s">
-        <v>753</v>
+      <c r="A29" s="20" t="s">
+        <v>1037</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>9</v>
@@ -5980,9 +6305,11 @@
       <c r="D29" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E29" s="38"/>
+      <c r="E29" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F29" s="21" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8" t="s">
@@ -5996,8 +6323,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.5">
-      <c r="A30" s="8" t="s">
-        <v>82</v>
+      <c r="A30" s="20" t="s">
+        <v>1038</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>19</v>
@@ -6008,10 +6335,12 @@
       <c r="D30" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="38"/>
+      <c r="E30" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F30" s="8"/>
       <c r="G30" s="21" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>82</v>
@@ -6024,8 +6353,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.5">
-      <c r="A31" s="8" t="s">
-        <v>757</v>
+      <c r="A31" s="20" t="s">
+        <v>1039</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>71</v>
@@ -6036,12 +6365,14 @@
       <c r="D31" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E31" s="38"/>
+      <c r="E31" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F31" s="20" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>717</v>
@@ -6053,20 +6384,19 @@
         <v>759</v>
       </c>
     </row>
-    <row r="32" spans="1:10"/>
     <row r="33" spans="1:10" ht="16.5">
-      <c r="A33" s="30" t="s">
-        <v>897</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32"/>
+      <c r="A33" s="37" t="s">
+        <v>894</v>
+      </c>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="39"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="7" t="s">
@@ -6083,7 +6413,7 @@
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7" t="s">
@@ -6109,12 +6439,14 @@
       <c r="D35" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E35" s="38"/>
+      <c r="E35" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F35" s="20" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>717</v>
@@ -6139,12 +6471,14 @@
       <c r="D36" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E36" s="38"/>
+      <c r="E36" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F36" s="20" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>717</v>
@@ -6157,8 +6491,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.5">
-      <c r="A37" s="8" t="s">
-        <v>61</v>
+      <c r="A37" s="20" t="s">
+        <v>1040</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>62</v>
@@ -6169,13 +6503,15 @@
       <c r="D37" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="38"/>
+      <c r="E37" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F37" s="23" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="G37" s="8"/>
-      <c r="H37" s="8" t="s">
-        <v>61</v>
+      <c r="H37" s="20" t="s">
+        <v>1040</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>760</v>
@@ -6185,8 +6521,8 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.5">
-      <c r="A38" s="8" t="s">
-        <v>68</v>
+      <c r="A38" s="20" t="s">
+        <v>1041</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>62</v>
@@ -6197,13 +6533,15 @@
       <c r="D38" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="38"/>
+      <c r="E38" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F38" s="23" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="G38" s="8"/>
-      <c r="H38" s="8" t="s">
-        <v>68</v>
+      <c r="H38" s="20" t="s">
+        <v>1041</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>762</v>
@@ -6212,20 +6550,19 @@
         <v>763</v>
       </c>
     </row>
-    <row r="39" spans="1:10"/>
     <row r="40" spans="1:10" ht="16.5">
-      <c r="A40" s="30" t="s">
-        <v>898</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="32"/>
+      <c r="A40" s="37" t="s">
+        <v>895</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="39"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="7" t="s">
@@ -6242,7 +6579,7 @@
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7" t="s">
@@ -6256,8 +6593,8 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="33">
-      <c r="A42" s="8" t="s">
-        <v>764</v>
+      <c r="A42" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>9</v>
@@ -6268,12 +6605,14 @@
       <c r="D42" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E42" s="38"/>
+      <c r="E42" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F42" s="20" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>717</v>
@@ -6298,12 +6637,14 @@
       <c r="D43" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E43" s="38"/>
+      <c r="E43" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F43" s="23" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>61</v>
@@ -6315,7 +6656,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16.5">
+    <row r="44" spans="1:10" ht="33">
       <c r="A44" s="8" t="s">
         <v>68</v>
       </c>
@@ -6328,11 +6669,15 @@
       <c r="D44" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="38"/>
+      <c r="E44" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F44" s="23" t="s">
-        <v>910</v>
-      </c>
-      <c r="G44" s="8"/>
+        <v>907</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>898</v>
+      </c>
       <c r="H44" s="8" t="s">
         <v>68</v>
       </c>
@@ -6343,20 +6688,19 @@
         <v>767</v>
       </c>
     </row>
-    <row r="45" spans="1:10"/>
     <row r="46" spans="1:10" ht="16.5">
-      <c r="A46" s="30" t="s">
-        <v>902</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="32"/>
+      <c r="A46" s="37" t="s">
+        <v>899</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="39"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="7" t="s">
@@ -6373,7 +6717,7 @@
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7" t="s">
@@ -6399,9 +6743,11 @@
       <c r="D48" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="38"/>
+      <c r="E48" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F48" s="21" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="G48" s="8"/>
       <c r="H48" s="8" t="s">
@@ -6415,8 +6761,8 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="49.5">
-      <c r="A49" s="8" t="s">
-        <v>73</v>
+      <c r="A49" s="20" t="s">
+        <v>1043</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>71</v>
@@ -6427,12 +6773,14 @@
       <c r="D49" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E49" s="38"/>
+      <c r="E49" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F49" s="21" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>717</v>
@@ -6446,7 +6794,7 @@
     </row>
     <row r="50" spans="1:10" ht="16.5">
       <c r="A50" s="20" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>45</v>
@@ -6457,9 +6805,11 @@
       <c r="D50" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="38"/>
+      <c r="E50" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F50" s="21" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="G50" s="21"/>
       <c r="H50" s="8" t="s">
@@ -6474,7 +6824,7 @@
     </row>
     <row r="51" spans="1:10" ht="16.5">
       <c r="A51" s="20" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>71</v>
@@ -6485,9 +6835,11 @@
       <c r="D51" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="38"/>
+      <c r="E51" s="30" t="s">
+        <v>1046</v>
+      </c>
       <c r="F51" s="21" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="G51" s="21"/>
       <c r="H51" s="8" t="s">
@@ -6500,20 +6852,19 @@
         <v>773</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17.25" customHeight="1"/>
     <row r="53" spans="1:10" ht="16.5">
-      <c r="A53" s="30" t="s">
-        <v>968</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="32"/>
+      <c r="A53" s="37" t="s">
+        <v>965</v>
+      </c>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="39"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="7" t="s">
@@ -6530,7 +6881,7 @@
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7" t="s">
@@ -6556,9 +6907,11 @@
       <c r="D55" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E55" s="38"/>
+      <c r="E55" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F55" s="20" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8" t="s">
@@ -6572,8 +6925,8 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="33">
-      <c r="A56" s="8" t="s">
-        <v>498</v>
+      <c r="A56" s="20" t="s">
+        <v>1044</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>340</v>
@@ -6584,12 +6937,14 @@
       <c r="D56" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E56" s="38"/>
+      <c r="E56" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F56" s="21" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>717</v>
@@ -6603,7 +6958,7 @@
     </row>
     <row r="57" spans="1:10" ht="16.5">
       <c r="A57" s="20" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>19</v>
@@ -6614,12 +6969,14 @@
       <c r="D57" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E57" s="38"/>
+      <c r="E57" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F57" s="21" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="H57" s="8" t="s">
         <v>95</v>
@@ -6632,8 +6989,8 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="66">
-      <c r="A58" s="8" t="s">
-        <v>776</v>
+      <c r="A58" s="20" t="s">
+        <v>1045</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>19</v>
@@ -6644,12 +7001,14 @@
       <c r="D58" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E58" s="38"/>
+      <c r="E58" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F58" s="26" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="H58" s="8" t="s">
         <v>717</v>
@@ -6663,7 +7022,7 @@
     </row>
     <row r="59" spans="1:10" ht="49.5">
       <c r="A59" s="20" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>19</v>
@@ -6674,15 +7033,17 @@
       <c r="D59" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E59" s="38"/>
+      <c r="E59" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F59" s="22" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="G59" s="20" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H59" s="20" t="s">
         <v>1005</v>
-      </c>
-      <c r="H59" s="20" t="s">
-        <v>1009</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>25</v>
@@ -6692,8 +7053,8 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="49.5">
-      <c r="A60" s="8" t="s">
-        <v>21</v>
+      <c r="A60" s="20" t="s">
+        <v>1047</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>27</v>
@@ -6704,15 +7065,17 @@
       <c r="D60" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E60" s="38"/>
+      <c r="E60" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F60" s="21" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="G60" s="20" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H60" s="20" t="s">
         <v>1006</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>1010</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>28</v>
@@ -6723,7 +7086,7 @@
     </row>
     <row r="61" spans="1:10" ht="16.5">
       <c r="A61" s="20" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>40</v>
@@ -6734,12 +7097,14 @@
       <c r="D61" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="38"/>
+      <c r="E61" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F61" s="21" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="G61" s="26" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="H61" s="8" t="s">
         <v>80</v>
@@ -6751,20 +7116,19 @@
         <v>782</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17.25" customHeight="1"/>
     <row r="63" spans="1:10" ht="16.5">
-      <c r="A63" s="30" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B63" s="31"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="32"/>
+      <c r="A63" s="37" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="39"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="7" t="s">
@@ -6781,7 +7145,7 @@
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7" t="s">
@@ -6807,7 +7171,9 @@
       <c r="D65" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E65" s="38"/>
+      <c r="E65" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8" t="s">
@@ -6817,12 +7183,12 @@
         <v>25</v>
       </c>
       <c r="J65" s="29" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16.5">
       <c r="A66" s="20" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>71</v>
@@ -6833,9 +7199,11 @@
       <c r="D66" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E66" s="38"/>
+      <c r="E66" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F66" s="22" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8" t="s">
@@ -6849,8 +7217,8 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="16.5">
-      <c r="A67" s="8" t="s">
-        <v>73</v>
+      <c r="A67" s="20" t="s">
+        <v>1043</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>74</v>
@@ -6859,12 +7227,16 @@
         <v>10</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>975</v>
-      </c>
-      <c r="E67" s="37"/>
-      <c r="F67" s="8"/>
+        <v>972</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>1053</v>
+      </c>
       <c r="G67" s="20" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="H67" s="8" t="s">
         <v>73</v>
@@ -6877,8 +7249,8 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.5">
-      <c r="A68" s="8" t="s">
-        <v>76</v>
+      <c r="A68" s="20" t="s">
+        <v>1048</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>19</v>
@@ -6889,9 +7261,11 @@
       <c r="D68" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E68" s="38"/>
+      <c r="E68" s="30" t="s">
+        <v>1035</v>
+      </c>
       <c r="F68" s="21" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="8" t="s">
@@ -6904,9 +7278,9 @@
         <v>786</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="16.5">
-      <c r="A69" s="8" t="s">
-        <v>84</v>
+    <row r="69" spans="1:10" ht="30">
+      <c r="A69" s="20" t="s">
+        <v>1049</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>27</v>
@@ -6917,10 +7291,14 @@
       <c r="D69" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E69" s="38"/>
-      <c r="F69" s="8"/>
+      <c r="E69" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>1051</v>
+      </c>
       <c r="G69" s="21" t="s">
-        <v>978</v>
+        <v>1050</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>84</v>
@@ -6933,8 +7311,8 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.5">
-      <c r="A70" s="8" t="s">
-        <v>90</v>
+      <c r="A70" s="20" t="s">
+        <v>1054</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>71</v>
@@ -6945,10 +7323,14 @@
       <c r="D70" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E70" s="38"/>
-      <c r="F70" s="8"/>
+      <c r="E70" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>1052</v>
+      </c>
       <c r="G70" s="21" t="s">
-        <v>978</v>
+        <v>1050</v>
       </c>
       <c r="H70" s="8" t="s">
         <v>90</v>
@@ -6960,20 +7342,19 @@
         <v>790</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17.25" customHeight="1"/>
     <row r="72" spans="1:10" ht="16.5">
-      <c r="A72" s="30" t="s">
+      <c r="A72" s="37" t="s">
         <v>791</v>
       </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="32"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="39"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="7" t="s">
@@ -6990,7 +7371,7 @@
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7" t="s">
@@ -7003,7 +7384,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" ht="30">
       <c r="A74" s="8" t="s">
         <v>792</v>
       </c>
@@ -7016,11 +7397,13 @@
       <c r="D74" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E74" s="38"/>
-      <c r="F74" s="8"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="20" t="s">
+        <v>1058</v>
+      </c>
       <c r="G74" s="8"/>
-      <c r="H74" s="8" t="s">
-        <v>53</v>
+      <c r="H74" s="20" t="s">
+        <v>1055</v>
       </c>
       <c r="I74" s="8" t="s">
         <v>55</v>
@@ -7029,9 +7412,9 @@
         <v>793</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="8" t="s">
-        <v>792</v>
+    <row r="75" spans="1:10" ht="30">
+      <c r="A75" s="20" t="s">
+        <v>1077</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>717</v>
@@ -7042,22 +7425,24 @@
       <c r="D75" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E75" s="38"/>
-      <c r="F75" s="8"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="20" t="s">
+        <v>1058</v>
+      </c>
       <c r="G75" s="8"/>
-      <c r="H75" s="8" t="s">
-        <v>87</v>
+      <c r="H75" s="20" t="s">
+        <v>1056</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="J75" s="8" t="s">
+      <c r="J75" s="20" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="30">
+      <c r="A76" s="8" t="s">
         <v>795</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="8" t="s">
-        <v>796</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>717</v>
@@ -7068,22 +7453,24 @@
       <c r="D76" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E76" s="38"/>
-      <c r="F76" s="8"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="20" t="s">
+        <v>1064</v>
+      </c>
       <c r="G76" s="8"/>
-      <c r="H76" s="8" t="s">
-        <v>92</v>
+      <c r="H76" s="20" t="s">
+        <v>1057</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J76" s="8" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" ht="30">
       <c r="A77" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>717</v>
@@ -7092,24 +7479,26 @@
         <v>717</v>
       </c>
       <c r="D77" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E77" s="31"/>
+      <c r="F77" s="20" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G77" s="8"/>
+      <c r="H77" s="20" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I77" s="8" t="s">
         <v>799</v>
-      </c>
-      <c r="E77" s="38"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>800</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" ht="30">
       <c r="A78" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>717</v>
@@ -7120,22 +7509,22 @@
       <c r="D78" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E78" s="38"/>
+      <c r="E78" s="31"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="20" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="J78" s="8" t="s">
         <v>802</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="8" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>717</v>
@@ -7146,33 +7535,34 @@
       <c r="D79" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E79" s="38"/>
-      <c r="F79" s="8"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="20" t="s">
+        <v>1046</v>
+      </c>
       <c r="G79" s="8"/>
-      <c r="H79" s="8" t="s">
-        <v>47</v>
+      <c r="H79" s="20" t="s">
+        <v>1061</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>48</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="17.25" customHeight="1"/>
+        <v>804</v>
+      </c>
+    </row>
     <row r="81" spans="1:10" ht="16.5">
-      <c r="A81" s="30" t="s">
-        <v>807</v>
-      </c>
-      <c r="B81" s="31"/>
-      <c r="C81" s="31"/>
-      <c r="D81" s="31"/>
-      <c r="E81" s="31"/>
-      <c r="F81" s="31"/>
-      <c r="G81" s="31"/>
-      <c r="H81" s="31"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="32"/>
+      <c r="A81" s="37" t="s">
+        <v>805</v>
+      </c>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="39"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="7" t="s">
@@ -7189,7 +7579,7 @@
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7" t="s">
@@ -7204,7 +7594,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="8" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>62</v>
@@ -7215,14 +7605,14 @@
       <c r="D83" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E83" s="38"/>
+      <c r="E83" s="31"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8" t="s">
         <v>717</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>719</v>
@@ -7241,7 +7631,7 @@
       <c r="D84" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E84" s="38"/>
+      <c r="E84" s="31"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="H84" s="8" t="s">
@@ -7265,24 +7655,24 @@
         <v>10</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="E85" s="38"/>
+        <v>808</v>
+      </c>
+      <c r="E85" s="31"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
-      <c r="H85" s="8" t="s">
-        <v>78</v>
+      <c r="H85" s="20" t="s">
+        <v>1062</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="8" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>560</v>
@@ -7293,31 +7683,30 @@
       <c r="D86" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E86" s="38"/>
+      <c r="E86" s="31"/>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8" t="s">
         <v>717</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="J86" s="8"/>
     </row>
-    <row r="87" spans="1:10" ht="17.25" customHeight="1"/>
     <row r="88" spans="1:10" ht="16.5">
-      <c r="A88" s="30" t="s">
-        <v>815</v>
-      </c>
-      <c r="B88" s="31"/>
-      <c r="C88" s="31"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="31"/>
-      <c r="H88" s="31"/>
-      <c r="I88" s="31"/>
-      <c r="J88" s="32"/>
+      <c r="A88" s="37" t="s">
+        <v>813</v>
+      </c>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
+      <c r="G88" s="38"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="38"/>
+      <c r="J88" s="39"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="7" t="s">
@@ -7334,7 +7723,7 @@
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7" t="s">
@@ -7358,19 +7747,19 @@
         <v>10</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>816</v>
-      </c>
-      <c r="E90" s="38"/>
+        <v>814</v>
+      </c>
+      <c r="E90" s="31"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
-      <c r="H90" s="8" t="s">
-        <v>97</v>
+      <c r="H90" s="20" t="s">
+        <v>1063</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -7378,7 +7767,7 @@
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
-      <c r="E91" s="40"/>
+      <c r="E91" s="33"/>
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
@@ -7390,27 +7779,26 @@
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
-      <c r="E92" s="40"/>
+      <c r="E92" s="33"/>
       <c r="F92" s="10"/>
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
     </row>
-    <row r="93" spans="1:10" ht="17.25" customHeight="1"/>
     <row r="94" spans="1:10" ht="16.5">
-      <c r="A94" s="30" t="s">
-        <v>818</v>
-      </c>
-      <c r="B94" s="31"/>
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="31"/>
-      <c r="F94" s="31"/>
-      <c r="G94" s="31"/>
-      <c r="H94" s="31"/>
-      <c r="I94" s="31"/>
-      <c r="J94" s="32"/>
+      <c r="A94" s="37" t="s">
+        <v>816</v>
+      </c>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="38"/>
+      <c r="J94" s="39"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="7" t="s">
@@ -7427,7 +7815,7 @@
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7" t="s">
@@ -7442,10 +7830,10 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="8" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>717</v>
@@ -7453,25 +7841,25 @@
       <c r="D96" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E96" s="38"/>
+      <c r="E96" s="31"/>
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
       <c r="H96" s="8" t="s">
         <v>21</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="8" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>717</v>
@@ -7479,51 +7867,51 @@
       <c r="D97" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E97" s="38"/>
+      <c r="E97" s="31"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8" t="s">
         <v>47</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="8" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>717</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>827</v>
-      </c>
-      <c r="E98" s="38"/>
+        <v>825</v>
+      </c>
+      <c r="E98" s="31"/>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="J98" s="8" t="s">
         <v>828</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>829</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="8" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>717</v>
@@ -7531,17 +7919,17 @@
       <c r="D99" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E99" s="38"/>
+      <c r="E99" s="31"/>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="20" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15.75" thickBot="1">
@@ -7549,16 +7937,16 @@
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
-      <c r="E100" s="40"/>
+      <c r="E100" s="33"/>
       <c r="F100" s="10"/>
       <c r="G100" s="10"/>
       <c r="H100" s="10"/>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
     </row>
-    <row r="101" spans="1:10" ht="21" thickBot="1">
+    <row r="101" spans="1:10" ht="41.25" thickBot="1">
       <c r="A101" s="17" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B101"/>
       <c r="C101" s="16"/>
@@ -7572,14 +7960,14 @@
     </row>
     <row r="102" spans="1:10" ht="18" thickBot="1">
       <c r="A102" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C102" s="15"/>
       <c r="D102" s="15"/>
-      <c r="E102" s="41"/>
+      <c r="E102" s="34"/>
       <c r="F102" s="15"/>
       <c r="G102" s="15"/>
       <c r="H102" s="15"/>
@@ -7591,11 +7979,11 @@
         <v>8</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15"/>
-      <c r="E103" s="41"/>
+      <c r="E103" s="34"/>
       <c r="F103" s="15"/>
       <c r="G103" s="15"/>
       <c r="H103" s="15"/>
@@ -7611,7 +7999,7 @@
       </c>
       <c r="C104" s="15"/>
       <c r="D104" s="15"/>
-      <c r="E104" s="41"/>
+      <c r="E104" s="34"/>
       <c r="F104" s="15"/>
       <c r="G104" s="15"/>
       <c r="H104" s="15"/>
@@ -7627,7 +8015,7 @@
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15"/>
-      <c r="E105" s="41"/>
+      <c r="E105" s="34"/>
       <c r="F105" s="15"/>
       <c r="G105" s="15"/>
       <c r="H105" s="15"/>
@@ -7636,14 +8024,14 @@
     </row>
     <row r="106" spans="1:10" ht="18" thickBot="1">
       <c r="A106" s="12" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C106" s="15"/>
       <c r="D106" s="15"/>
-      <c r="E106" s="41"/>
+      <c r="E106" s="34"/>
       <c r="F106" s="15"/>
       <c r="G106" s="15"/>
       <c r="H106" s="15"/>
@@ -7655,21 +8043,21 @@
       <c r="B107" s="18"/>
       <c r="C107" s="15"/>
       <c r="D107" s="15"/>
-      <c r="E107" s="41"/>
+      <c r="E107" s="34"/>
       <c r="F107" s="15"/>
       <c r="G107" s="15"/>
       <c r="H107" s="15"/>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
     </row>
-    <row r="108" spans="1:10" ht="21" thickBot="1">
+    <row r="108" spans="1:10" ht="41.25" thickBot="1">
       <c r="A108" s="17" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B108"/>
       <c r="C108" s="15"/>
       <c r="D108" s="15"/>
-      <c r="E108" s="41"/>
+      <c r="E108" s="34"/>
       <c r="F108" s="15"/>
       <c r="G108" s="15"/>
       <c r="H108" s="15"/>
@@ -7678,14 +8066,14 @@
     </row>
     <row r="109" spans="1:10" ht="18" thickBot="1">
       <c r="A109" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15"/>
-      <c r="E109" s="41"/>
+      <c r="E109" s="34"/>
       <c r="F109" s="15"/>
       <c r="G109" s="15"/>
       <c r="H109" s="15"/>
@@ -7697,40 +8085,40 @@
         <v>13</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C110" s="15"/>
       <c r="D110" s="15"/>
-      <c r="E110" s="41"/>
+      <c r="E110" s="34"/>
       <c r="F110" s="15"/>
       <c r="G110" s="15"/>
       <c r="H110" s="15"/>
       <c r="I110" s="10"/>
       <c r="J110" s="10"/>
     </row>
-    <row r="111" spans="1:10" ht="17.25" customHeight="1" thickBot="1">
+    <row r="111" spans="1:10" ht="18" thickBot="1">
       <c r="A111" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C111" s="15"/>
       <c r="D111" s="15"/>
-      <c r="E111" s="41"/>
+      <c r="E111" s="34"/>
       <c r="F111" s="15"/>
       <c r="G111" s="15"/>
       <c r="H111" s="15"/>
     </row>
-    <row r="112" spans="1:10" ht="17.25" customHeight="1" thickBot="1">
+    <row r="112" spans="1:10" ht="18" thickBot="1">
       <c r="A112" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="18" thickBot="1">
       <c r="A113" s="12" t="s">
         <v>18</v>
       </c>
@@ -7739,11 +8127,11 @@
       </c>
       <c r="C113" s="16"/>
       <c r="D113" s="13"/>
-      <c r="E113" s="36"/>
+      <c r="E113" s="19"/>
       <c r="F113" s="19"/>
       <c r="G113" s="19"/>
     </row>
-    <row r="114" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="114" spans="1:7" ht="18" thickBot="1">
       <c r="A114" s="12" t="s">
         <v>44</v>
       </c>
@@ -7752,11 +8140,11 @@
       </c>
       <c r="C114" s="12"/>
       <c r="D114" s="12"/>
-      <c r="E114" s="42"/>
+      <c r="E114" s="35"/>
       <c r="F114" s="18"/>
       <c r="G114" s="18"/>
     </row>
-    <row r="115" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="115" spans="1:7" ht="18" thickBot="1">
       <c r="A115" s="12" t="s">
         <v>29</v>
       </c>
@@ -7765,11 +8153,11 @@
       </c>
       <c r="C115" s="12"/>
       <c r="D115" s="12"/>
-      <c r="E115" s="42"/>
+      <c r="E115" s="35"/>
       <c r="F115" s="18"/>
       <c r="G115" s="18"/>
     </row>
-    <row r="116" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="116" spans="1:7" ht="18" thickBot="1">
       <c r="A116" s="12" t="s">
         <v>31</v>
       </c>
@@ -7778,11 +8166,11 @@
       </c>
       <c r="C116" s="12"/>
       <c r="D116" s="12"/>
-      <c r="E116" s="42"/>
+      <c r="E116" s="35"/>
       <c r="F116" s="18"/>
       <c r="G116" s="18"/>
     </row>
-    <row r="117" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="117" spans="1:7" ht="18" thickBot="1">
       <c r="A117" s="12" t="s">
         <v>33</v>
       </c>
@@ -7791,24 +8179,24 @@
       </c>
       <c r="C117" s="12"/>
       <c r="D117" s="12"/>
-      <c r="E117" s="42"/>
+      <c r="E117" s="35"/>
       <c r="F117" s="18"/>
       <c r="G117" s="18"/>
     </row>
-    <row r="118" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="118" spans="1:7" ht="18" thickBot="1">
       <c r="A118" s="12" t="s">
         <v>35</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C118" s="12"/>
       <c r="D118" s="12"/>
-      <c r="E118" s="42"/>
+      <c r="E118" s="35"/>
       <c r="F118" s="18"/>
       <c r="G118" s="18"/>
     </row>
-    <row r="119" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="119" spans="1:7" ht="18" thickBot="1">
       <c r="A119" s="12" t="s">
         <v>735</v>
       </c>
@@ -7817,57 +8205,57 @@
       </c>
       <c r="C119" s="12"/>
       <c r="D119" s="12"/>
-      <c r="E119" s="42"/>
+      <c r="E119" s="35"/>
       <c r="F119" s="18"/>
       <c r="G119" s="18"/>
     </row>
-    <row r="120" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="120" spans="1:7" ht="18" thickBot="1">
       <c r="A120" s="18"/>
       <c r="B120" s="18"/>
       <c r="C120" s="12"/>
       <c r="D120" s="12"/>
-      <c r="E120" s="42"/>
+      <c r="E120" s="35"/>
       <c r="F120" s="18"/>
       <c r="G120" s="18"/>
     </row>
-    <row r="121" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="121" spans="1:7" ht="41.25" thickBot="1">
       <c r="A121" s="17" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B121"/>
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
-      <c r="E121" s="42"/>
+      <c r="E121" s="35"/>
       <c r="F121" s="18"/>
       <c r="G121" s="18"/>
     </row>
-    <row r="122" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="122" spans="1:7" ht="18" thickBot="1">
       <c r="A122" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C122" s="12"/>
       <c r="D122" s="12"/>
-      <c r="E122" s="42"/>
+      <c r="E122" s="35"/>
       <c r="F122" s="18"/>
       <c r="G122" s="18"/>
     </row>
-    <row r="123" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="123" spans="1:7" ht="18" thickBot="1">
       <c r="A123" s="12" t="s">
-        <v>35</v>
+        <v>1028</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C123" s="12"/>
       <c r="D123" s="12"/>
-      <c r="E123" s="42"/>
+      <c r="E123" s="35"/>
       <c r="F123" s="18"/>
       <c r="G123" s="18"/>
     </row>
-    <row r="124" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="124" spans="1:7" ht="18" thickBot="1">
       <c r="A124" s="12" t="s">
         <v>37</v>
       </c>
@@ -7876,50 +8264,50 @@
       </c>
       <c r="C124" s="12"/>
       <c r="D124" s="12"/>
-      <c r="E124" s="42"/>
+      <c r="E124" s="35"/>
       <c r="F124" s="18"/>
       <c r="G124" s="18"/>
     </row>
-    <row r="125" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="125" spans="1:7" ht="18" thickBot="1">
       <c r="A125" s="12" t="s">
         <v>751</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C125" s="12"/>
       <c r="D125" s="12"/>
-      <c r="E125" s="42"/>
+      <c r="E125" s="35"/>
       <c r="F125" s="18"/>
       <c r="G125" s="18"/>
     </row>
-    <row r="126" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="126" spans="1:7" ht="18" thickBot="1">
       <c r="A126" s="12" t="s">
         <v>753</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C126" s="12"/>
       <c r="D126" s="12"/>
-      <c r="E126" s="42"/>
+      <c r="E126" s="35"/>
       <c r="F126" s="18"/>
       <c r="G126" s="18"/>
     </row>
-    <row r="127" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="127" spans="1:7" ht="18" thickBot="1">
       <c r="A127" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C127" s="12"/>
       <c r="D127" s="12"/>
-      <c r="E127" s="42"/>
+      <c r="E127" s="35"/>
       <c r="F127" s="18"/>
       <c r="G127" s="18"/>
     </row>
-    <row r="128" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="128" spans="1:7" ht="18" thickBot="1">
       <c r="A128" s="12" t="s">
         <v>59</v>
       </c>
@@ -7928,11 +8316,11 @@
       </c>
       <c r="C128" s="12"/>
       <c r="D128" s="12"/>
-      <c r="E128" s="42"/>
+      <c r="E128" s="35"/>
       <c r="F128" s="18"/>
       <c r="G128" s="18"/>
     </row>
-    <row r="129" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="129" spans="1:7" ht="18" thickBot="1">
       <c r="A129" s="12" t="s">
         <v>64</v>
       </c>
@@ -7941,11 +8329,11 @@
       </c>
       <c r="C129" s="12"/>
       <c r="D129" s="12"/>
-      <c r="E129" s="42"/>
+      <c r="E129" s="35"/>
       <c r="F129" s="18"/>
       <c r="G129" s="18"/>
     </row>
-    <row r="130" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="130" spans="1:7" ht="18" thickBot="1">
       <c r="A130" s="12" t="s">
         <v>42</v>
       </c>
@@ -7954,11 +8342,11 @@
       </c>
       <c r="C130" s="12"/>
       <c r="D130" s="12"/>
-      <c r="E130" s="42"/>
+      <c r="E130" s="35"/>
       <c r="F130" s="18"/>
       <c r="G130" s="18"/>
     </row>
-    <row r="131" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="131" spans="1:7" ht="18" thickBot="1">
       <c r="A131" s="12" t="s">
         <v>82</v>
       </c>
@@ -7967,96 +8355,96 @@
       </c>
       <c r="C131" s="12"/>
       <c r="D131" s="12"/>
-      <c r="E131" s="42"/>
+      <c r="E131" s="35"/>
       <c r="F131" s="18"/>
       <c r="G131" s="18"/>
     </row>
-    <row r="132" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="132" spans="1:7" ht="18" thickBot="1">
       <c r="A132" s="12" t="s">
         <v>757</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C132" s="12"/>
       <c r="D132" s="12"/>
-      <c r="E132" s="42"/>
+      <c r="E132" s="35"/>
       <c r="F132" s="18"/>
       <c r="G132" s="18"/>
     </row>
-    <row r="133" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="133" spans="1:7" ht="18" thickBot="1">
       <c r="A133" s="18"/>
       <c r="B133" s="18"/>
       <c r="C133" s="12"/>
       <c r="D133" s="12"/>
-      <c r="E133" s="42"/>
+      <c r="E133" s="35"/>
       <c r="F133" s="18"/>
       <c r="G133" s="18"/>
     </row>
-    <row r="134" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="134" spans="1:7" ht="41.25" thickBot="1">
       <c r="A134" s="17" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B134"/>
       <c r="C134" s="12"/>
       <c r="D134" s="12"/>
-      <c r="E134" s="42"/>
+      <c r="E134" s="35"/>
       <c r="F134" s="18"/>
       <c r="G134" s="18"/>
     </row>
-    <row r="135" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="135" spans="1:7" ht="18" thickBot="1">
       <c r="A135" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C135" s="12"/>
       <c r="D135" s="12"/>
-      <c r="E135" s="42"/>
+      <c r="E135" s="35"/>
       <c r="F135" s="18"/>
       <c r="G135" s="18"/>
     </row>
-    <row r="136" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="136" spans="1:7" ht="18" thickBot="1">
       <c r="A136" s="12" t="s">
         <v>751</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C136" s="12"/>
       <c r="D136" s="12"/>
-      <c r="E136" s="42"/>
+      <c r="E136" s="35"/>
       <c r="F136" s="18"/>
       <c r="G136" s="18"/>
     </row>
-    <row r="137" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="137" spans="1:7" ht="18" thickBot="1">
       <c r="A137" s="12" t="s">
         <v>753</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C137" s="12"/>
       <c r="D137" s="12"/>
-      <c r="E137" s="42"/>
+      <c r="E137" s="35"/>
       <c r="F137" s="18"/>
       <c r="G137" s="18"/>
     </row>
-    <row r="138" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="138" spans="1:7" ht="18" thickBot="1">
       <c r="A138" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C138" s="12"/>
       <c r="D138" s="12"/>
-      <c r="E138" s="42"/>
+      <c r="E138" s="35"/>
       <c r="F138" s="18"/>
       <c r="G138" s="18"/>
     </row>
-    <row r="139" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="139" spans="1:7" ht="18" thickBot="1">
       <c r="A139" s="12" t="s">
         <v>68</v>
       </c>
@@ -8065,70 +8453,70 @@
       </c>
       <c r="C139" s="12"/>
       <c r="D139" s="12"/>
-      <c r="E139" s="42"/>
+      <c r="E139" s="35"/>
       <c r="F139" s="18"/>
       <c r="G139" s="18"/>
     </row>
-    <row r="140" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="140" spans="1:7" ht="18" thickBot="1">
       <c r="A140" s="18"/>
       <c r="B140" s="18"/>
       <c r="C140" s="12"/>
       <c r="D140" s="12"/>
-      <c r="E140" s="42"/>
+      <c r="E140" s="35"/>
       <c r="F140" s="18"/>
       <c r="G140" s="18"/>
     </row>
-    <row r="141" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="141" spans="1:7" ht="41.25" thickBot="1">
       <c r="A141" s="17" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B141"/>
       <c r="C141" s="12"/>
       <c r="D141" s="12"/>
-      <c r="E141" s="42"/>
+      <c r="E141" s="35"/>
       <c r="F141" s="18"/>
       <c r="G141" s="18"/>
     </row>
-    <row r="142" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="142" spans="1:7" ht="18" thickBot="1">
       <c r="A142" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C142" s="12"/>
       <c r="D142" s="12"/>
-      <c r="E142" s="42"/>
+      <c r="E142" s="35"/>
       <c r="F142" s="18"/>
       <c r="G142" s="18"/>
     </row>
-    <row r="143" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="143" spans="1:7" ht="18" thickBot="1">
       <c r="A143" s="12" t="s">
         <v>764</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
-      <c r="E143" s="42"/>
+      <c r="E143" s="35"/>
       <c r="F143" s="18"/>
       <c r="G143" s="18"/>
     </row>
-    <row r="144" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="144" spans="1:7" ht="18" thickBot="1">
       <c r="A144" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C144" s="12"/>
       <c r="D144" s="12"/>
-      <c r="E144" s="42"/>
+      <c r="E144" s="35"/>
       <c r="F144" s="18"/>
       <c r="G144" s="18"/>
     </row>
-    <row r="145" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="145" spans="1:7" ht="18" thickBot="1">
       <c r="A145" s="12" t="s">
         <v>68</v>
       </c>
@@ -8137,44 +8525,44 @@
       </c>
       <c r="C145" s="12"/>
       <c r="D145" s="12"/>
-      <c r="E145" s="42"/>
+      <c r="E145" s="35"/>
       <c r="F145" s="18"/>
       <c r="G145" s="18"/>
     </row>
-    <row r="146" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="146" spans="1:7" ht="18" thickBot="1">
       <c r="A146" s="18"/>
       <c r="B146" s="18"/>
       <c r="C146" s="12"/>
       <c r="D146" s="12"/>
-      <c r="E146" s="42"/>
+      <c r="E146" s="35"/>
       <c r="F146" s="18"/>
       <c r="G146" s="18"/>
     </row>
-    <row r="147" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="147" spans="1:7" ht="21" thickBot="1">
       <c r="A147" s="17" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B147"/>
       <c r="C147" s="12"/>
       <c r="D147" s="12"/>
-      <c r="E147" s="42"/>
+      <c r="E147" s="35"/>
       <c r="F147" s="18"/>
       <c r="G147" s="18"/>
     </row>
-    <row r="148" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="148" spans="1:7" ht="18" thickBot="1">
       <c r="A148" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C148" s="12"/>
       <c r="D148" s="12"/>
-      <c r="E148" s="42"/>
+      <c r="E148" s="35"/>
       <c r="F148" s="18"/>
       <c r="G148" s="18"/>
     </row>
-    <row r="149" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="149" spans="1:7" ht="18" thickBot="1">
       <c r="A149" s="12" t="s">
         <v>18</v>
       </c>
@@ -8183,11 +8571,11 @@
       </c>
       <c r="C149" s="12"/>
       <c r="D149" s="12"/>
-      <c r="E149" s="42"/>
+      <c r="E149" s="35"/>
       <c r="F149" s="18"/>
       <c r="G149" s="18"/>
     </row>
-    <row r="150" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="150" spans="1:7" ht="18" thickBot="1">
       <c r="A150" s="12" t="s">
         <v>73</v>
       </c>
@@ -8196,11 +8584,11 @@
       </c>
       <c r="C150" s="12"/>
       <c r="D150" s="12"/>
-      <c r="E150" s="42"/>
+      <c r="E150" s="35"/>
       <c r="F150" s="18"/>
       <c r="G150" s="18"/>
     </row>
-    <row r="151" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="151" spans="1:7" ht="18" thickBot="1">
       <c r="A151" s="12" t="s">
         <v>98</v>
       </c>
@@ -8209,60 +8597,60 @@
       </c>
       <c r="C151" s="12"/>
       <c r="D151" s="12"/>
-      <c r="E151" s="42"/>
+      <c r="E151" s="35"/>
       <c r="F151" s="18"/>
       <c r="G151" s="18"/>
     </row>
-    <row r="152" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="152" spans="1:7" ht="18" thickBot="1">
       <c r="A152" s="12" t="s">
         <v>100</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C152" s="12"/>
       <c r="D152" s="12"/>
-      <c r="E152" s="42"/>
+      <c r="E152" s="35"/>
       <c r="F152" s="18"/>
       <c r="G152" s="18"/>
     </row>
-    <row r="153" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="153" spans="1:7" ht="18" thickBot="1">
       <c r="A153" s="18"/>
       <c r="B153" s="18"/>
       <c r="C153" s="12"/>
       <c r="D153" s="12"/>
-      <c r="E153" s="42"/>
+      <c r="E153" s="35"/>
       <c r="F153" s="18"/>
       <c r="G153" s="18"/>
     </row>
-    <row r="154" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="154" spans="1:7" ht="41.25" thickBot="1">
       <c r="A154" s="17" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B154"/>
       <c r="C154" s="12"/>
       <c r="D154" s="12"/>
-      <c r="E154" s="42"/>
+      <c r="E154" s="35"/>
       <c r="F154" s="18"/>
       <c r="G154" s="18"/>
     </row>
-    <row r="155" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="155" spans="1:7" ht="18" thickBot="1">
       <c r="A155" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="18" thickBot="1">
       <c r="A156" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="18" thickBot="1">
       <c r="A157" s="12" t="s">
         <v>68</v>
       </c>
@@ -8270,41 +8658,41 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="158" spans="1:7" ht="18" thickBot="1">
       <c r="A158" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="17.25" customHeight="1">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="17.25">
       <c r="A159" s="18"/>
       <c r="B159" s="18"/>
     </row>
-    <row r="160" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
+    <row r="160" spans="1:7" ht="41.25" thickBot="1">
       <c r="A160" s="17" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B160"/>
     </row>
-    <row r="161" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="161" spans="1:2" ht="18" thickBot="1">
       <c r="A161" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="18" thickBot="1">
       <c r="A162" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="18" thickBot="1">
       <c r="A163" s="12" t="s">
         <v>498</v>
       </c>
@@ -8312,7 +8700,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="164" spans="1:2" ht="18" thickBot="1">
       <c r="A164" s="12" t="s">
         <v>95</v>
       </c>
@@ -8320,7 +8708,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="165" spans="1:2" ht="18" thickBot="1">
       <c r="A165" s="12" t="s">
         <v>776</v>
       </c>
@@ -8328,7 +8716,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="166" spans="1:2" ht="18" thickBot="1">
       <c r="A166" s="12" t="s">
         <v>18</v>
       </c>
@@ -8336,7 +8724,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="167" spans="1:2" ht="18" thickBot="1">
       <c r="A167" s="12" t="s">
         <v>21</v>
       </c>
@@ -8344,7 +8732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="168" spans="1:2" ht="18" thickBot="1">
       <c r="A168" s="12" t="s">
         <v>80</v>
       </c>
@@ -8352,65 +8740,65 @@
         <v>81</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="17.25" customHeight="1">
+    <row r="169" spans="1:2" ht="17.25">
       <c r="A169" s="18"/>
       <c r="B169" s="18"/>
     </row>
-    <row r="170" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="170" spans="1:2" ht="41.25" thickBot="1">
       <c r="A170" s="17" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B170"/>
     </row>
-    <row r="171" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="171" spans="1:2" ht="18" thickBot="1">
       <c r="A171" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="18" thickBot="1">
       <c r="A172" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="18" thickBot="1">
       <c r="A173" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="18" thickBot="1">
       <c r="A174" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="18" thickBot="1">
       <c r="A175" s="12" t="s">
         <v>76</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="18" thickBot="1">
       <c r="A176" s="12" t="s">
         <v>84</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="18" thickBot="1">
       <c r="A177" s="12" t="s">
         <v>90</v>
       </c>
@@ -8418,91 +8806,91 @@
         <v>789</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="17.25" customHeight="1">
+    <row r="178" spans="1:2" ht="17.25">
       <c r="A178" s="18"/>
       <c r="B178" s="18"/>
     </row>
-    <row r="179" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="179" spans="1:2" ht="41.25" thickBot="1">
       <c r="A179" s="17" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B179"/>
     </row>
-    <row r="180" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="180" spans="1:2" ht="18" thickBot="1">
       <c r="A180" s="11" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="18" thickBot="1">
       <c r="A181" s="12" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="182" spans="1:2" ht="18" thickBot="1">
       <c r="A182" s="12" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="183" spans="1:2" ht="35.25" thickBot="1">
       <c r="A183" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="35.25" thickBot="1">
+      <c r="A184" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="B183" s="12" t="s">
+      <c r="B184" s="12" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A184" s="12" t="s">
+    <row r="185" spans="1:2" ht="18" thickBot="1">
+      <c r="A185" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="B184" s="12" t="s">
+      <c r="B185" s="12" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A185" s="12" t="s">
-        <v>867</v>
-      </c>
-      <c r="B185" s="12" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" ht="17.25" customHeight="1">
+    <row r="186" spans="1:2" ht="17.25">
       <c r="A186" s="18"/>
       <c r="B186" s="18"/>
     </row>
-    <row r="187" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="187" spans="1:2" ht="41.25" thickBot="1">
       <c r="A187" s="17" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B187"/>
     </row>
-    <row r="188" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="188" spans="1:2" ht="18" thickBot="1">
       <c r="A188" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="18" thickBot="1">
       <c r="A189" s="12" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="18" thickBot="1">
       <c r="A190" s="12" t="s">
         <v>68</v>
       </c>
@@ -8510,843 +8898,22 @@
         <v>69</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+    <row r="191" spans="1:2" ht="18" thickBot="1">
       <c r="A191" s="12" t="s">
         <v>78</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" ht="17.25" customHeight="1" thickBot="1">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="18" thickBot="1">
       <c r="A192" s="12" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="193" ht="17.25" customHeight="1"/>
-    <row r="194" ht="17.25" customHeight="1"/>
-    <row r="195" ht="17.25" customHeight="1"/>
-    <row r="196" ht="17.25" customHeight="1"/>
-    <row r="197" ht="17.25" customHeight="1"/>
-    <row r="198" ht="17.25" customHeight="1"/>
-    <row r="199" ht="17.25" customHeight="1"/>
-    <row r="200" ht="17.25" customHeight="1"/>
-    <row r="201" ht="17.25" customHeight="1"/>
-    <row r="202" ht="17.25" customHeight="1"/>
-    <row r="203" ht="17.25" customHeight="1"/>
-    <row r="204" ht="17.25" customHeight="1"/>
-    <row r="205" ht="17.25" customHeight="1"/>
-    <row r="206" ht="17.25" customHeight="1"/>
-    <row r="207" ht="17.25" customHeight="1"/>
-    <row r="208" ht="17.25" customHeight="1"/>
-    <row r="209" ht="17.25" customHeight="1"/>
-    <row r="210" ht="17.25" customHeight="1"/>
-    <row r="211" ht="17.25" customHeight="1"/>
-    <row r="212" ht="17.25" customHeight="1"/>
-    <row r="213" ht="17.25" customHeight="1"/>
-    <row r="214" ht="17.25" customHeight="1"/>
-    <row r="215" ht="17.25" customHeight="1"/>
-    <row r="216" ht="17.25" customHeight="1"/>
-    <row r="217" ht="17.25" customHeight="1"/>
-    <row r="218" ht="17.25" customHeight="1"/>
-    <row r="219" ht="17.25" customHeight="1"/>
-    <row r="220" ht="17.25" customHeight="1"/>
-    <row r="221" ht="17.25" customHeight="1"/>
-    <row r="222" ht="17.25" customHeight="1"/>
-    <row r="223" ht="17.25" customHeight="1"/>
-    <row r="224" ht="17.25" customHeight="1"/>
-    <row r="225" ht="17.25" customHeight="1"/>
-    <row r="226" ht="17.25" customHeight="1"/>
-    <row r="227" ht="17.25" customHeight="1"/>
-    <row r="228" ht="17.25" customHeight="1"/>
-    <row r="229" ht="17.25" customHeight="1"/>
-    <row r="230" ht="17.25" customHeight="1"/>
-    <row r="231" ht="17.25" customHeight="1"/>
-    <row r="232" ht="17.25" customHeight="1"/>
-    <row r="233" ht="17.25" customHeight="1"/>
-    <row r="234" ht="17.25" customHeight="1"/>
-    <row r="235" ht="17.25" customHeight="1"/>
-    <row r="236" ht="17.25" customHeight="1"/>
-    <row r="237" ht="17.25" customHeight="1"/>
-    <row r="238" ht="17.25" customHeight="1"/>
-    <row r="239" ht="17.25" customHeight="1"/>
-    <row r="240" ht="17.25" customHeight="1"/>
-    <row r="241" ht="17.25" customHeight="1"/>
-    <row r="242" ht="17.25" customHeight="1"/>
-    <row r="243" ht="17.25" customHeight="1"/>
-    <row r="244" ht="17.25" customHeight="1"/>
-    <row r="245" ht="17.25" customHeight="1"/>
-    <row r="246" ht="17.25" customHeight="1"/>
-    <row r="247" ht="17.25" customHeight="1"/>
-    <row r="248" ht="17.25" customHeight="1"/>
-    <row r="249" ht="17.25" customHeight="1"/>
-    <row r="250" ht="17.25" customHeight="1"/>
-    <row r="251" ht="17.25" customHeight="1"/>
-    <row r="252" ht="17.25" customHeight="1"/>
-    <row r="253" ht="17.25" customHeight="1"/>
-    <row r="254" ht="17.25" customHeight="1"/>
-    <row r="255" ht="17.25" customHeight="1"/>
-    <row r="256" ht="17.25" customHeight="1"/>
-    <row r="257" ht="17.25" customHeight="1"/>
-    <row r="258" ht="17.25" customHeight="1"/>
-    <row r="259" ht="17.25" customHeight="1"/>
-    <row r="260" ht="17.25" customHeight="1"/>
-    <row r="261" ht="17.25" customHeight="1"/>
-    <row r="262" ht="17.25" customHeight="1"/>
-    <row r="263" ht="17.25" customHeight="1"/>
-    <row r="264" ht="17.25" customHeight="1"/>
-    <row r="265" ht="17.25" customHeight="1"/>
-    <row r="266" ht="17.25" customHeight="1"/>
-    <row r="267" ht="17.25" customHeight="1"/>
-    <row r="268" ht="17.25" customHeight="1"/>
-    <row r="269" ht="17.25" customHeight="1"/>
-    <row r="270" ht="17.25" customHeight="1"/>
-    <row r="271" ht="17.25" customHeight="1"/>
-    <row r="272" ht="17.25" customHeight="1"/>
-    <row r="273" ht="17.25" customHeight="1"/>
-    <row r="274" ht="17.25" customHeight="1"/>
-    <row r="275" ht="17.25" customHeight="1"/>
-    <row r="276" ht="17.25" customHeight="1"/>
-    <row r="277" ht="17.25" customHeight="1"/>
-    <row r="278" ht="17.25" customHeight="1"/>
-    <row r="279" ht="17.25" customHeight="1"/>
-    <row r="280" ht="17.25" customHeight="1"/>
-    <row r="281" ht="17.25" customHeight="1"/>
-    <row r="282" ht="17.25" customHeight="1"/>
-    <row r="283" ht="17.25" customHeight="1"/>
-    <row r="284" ht="17.25" customHeight="1"/>
-    <row r="285" ht="17.25" customHeight="1"/>
-    <row r="286" ht="17.25" customHeight="1"/>
-    <row r="287" ht="17.25" customHeight="1"/>
-    <row r="288" ht="17.25" customHeight="1"/>
-    <row r="289" ht="17.25" customHeight="1"/>
-    <row r="290" ht="17.25" customHeight="1"/>
-    <row r="291" ht="17.25" customHeight="1"/>
-    <row r="292" ht="17.25" customHeight="1"/>
-    <row r="293" ht="17.25" customHeight="1"/>
-    <row r="294" ht="17.25" customHeight="1"/>
-    <row r="295" ht="17.25" customHeight="1"/>
-    <row r="296" ht="17.25" customHeight="1"/>
-    <row r="297" ht="17.25" customHeight="1"/>
-    <row r="298" ht="17.25" customHeight="1"/>
-    <row r="299" ht="17.25" customHeight="1"/>
-    <row r="300" ht="17.25" customHeight="1"/>
-    <row r="301" ht="17.25" customHeight="1"/>
-    <row r="302" ht="17.25" customHeight="1"/>
-    <row r="303" ht="17.25" customHeight="1"/>
-    <row r="304" ht="17.25" customHeight="1"/>
-    <row r="305" ht="17.25" customHeight="1"/>
-    <row r="306" ht="17.25" customHeight="1"/>
-    <row r="307" ht="17.25" customHeight="1"/>
-    <row r="308" ht="17.25" customHeight="1"/>
-    <row r="309" ht="17.25" customHeight="1"/>
-    <row r="310" ht="17.25" customHeight="1"/>
-    <row r="311" ht="17.25" customHeight="1"/>
-    <row r="312" ht="17.25" customHeight="1"/>
-    <row r="313" ht="17.25" customHeight="1"/>
-    <row r="314" ht="17.25" customHeight="1"/>
-    <row r="315" ht="17.25" customHeight="1"/>
-    <row r="316" ht="17.25" customHeight="1"/>
-    <row r="317" ht="17.25" customHeight="1"/>
-    <row r="318" ht="17.25" customHeight="1"/>
-    <row r="319" ht="17.25" customHeight="1"/>
-    <row r="320" ht="17.25" customHeight="1"/>
-    <row r="321" ht="17.25" customHeight="1"/>
-    <row r="322" ht="17.25" customHeight="1"/>
-    <row r="323" ht="17.25" customHeight="1"/>
-    <row r="324" ht="17.25" customHeight="1"/>
-    <row r="325" ht="17.25" customHeight="1"/>
-    <row r="326" ht="17.25" customHeight="1"/>
-    <row r="327" ht="17.25" customHeight="1"/>
-    <row r="328" ht="17.25" customHeight="1"/>
-    <row r="329" ht="17.25" customHeight="1"/>
-    <row r="330" ht="17.25" customHeight="1"/>
-    <row r="331" ht="17.25" customHeight="1"/>
-    <row r="332" ht="17.25" customHeight="1"/>
-    <row r="333" ht="17.25" customHeight="1"/>
-    <row r="334" ht="17.25" customHeight="1"/>
-    <row r="335" ht="17.25" customHeight="1"/>
-    <row r="336" ht="17.25" customHeight="1"/>
-    <row r="337" ht="17.25" customHeight="1"/>
-    <row r="338" ht="17.25" customHeight="1"/>
-    <row r="339" ht="17.25" customHeight="1"/>
-    <row r="340" ht="17.25" customHeight="1"/>
-    <row r="341" ht="17.25" customHeight="1"/>
-    <row r="342" ht="17.25" customHeight="1"/>
-    <row r="343" ht="17.25" customHeight="1"/>
-    <row r="344" ht="17.25" customHeight="1"/>
-    <row r="345" ht="17.25" customHeight="1"/>
-    <row r="346" ht="17.25" customHeight="1"/>
-    <row r="347" ht="17.25" customHeight="1"/>
-    <row r="348" ht="17.25" customHeight="1"/>
-    <row r="349" ht="17.25" customHeight="1"/>
-    <row r="350" ht="17.25" customHeight="1"/>
-    <row r="351" ht="17.25" customHeight="1"/>
-    <row r="352" ht="17.25" customHeight="1"/>
-    <row r="353" ht="17.25" customHeight="1"/>
-    <row r="354" ht="17.25" customHeight="1"/>
-    <row r="355" ht="17.25" customHeight="1"/>
-    <row r="356" ht="17.25" customHeight="1"/>
-    <row r="357" ht="17.25" customHeight="1"/>
-    <row r="358" ht="17.25" customHeight="1"/>
-    <row r="359" ht="17.25" customHeight="1"/>
-    <row r="360" ht="17.25" customHeight="1"/>
-    <row r="361" ht="17.25" customHeight="1"/>
-    <row r="362" ht="17.25" customHeight="1"/>
-    <row r="363" ht="17.25" customHeight="1"/>
-    <row r="364" ht="17.25" customHeight="1"/>
-    <row r="365" ht="17.25" customHeight="1"/>
-    <row r="366" ht="17.25" customHeight="1"/>
-    <row r="367" ht="17.25" customHeight="1"/>
-    <row r="368" ht="17.25" customHeight="1"/>
-    <row r="369" ht="17.25" customHeight="1"/>
-    <row r="370" ht="17.25" customHeight="1"/>
-    <row r="371" ht="17.25" customHeight="1"/>
-    <row r="372" ht="17.25" customHeight="1"/>
-    <row r="373" ht="17.25" customHeight="1"/>
-    <row r="374" ht="17.25" customHeight="1"/>
-    <row r="375" ht="17.25" customHeight="1"/>
-    <row r="376" ht="17.25" customHeight="1"/>
-    <row r="377" ht="17.25" customHeight="1"/>
-    <row r="378" ht="17.25" customHeight="1"/>
-    <row r="379" ht="17.25" customHeight="1"/>
-    <row r="380" ht="17.25" customHeight="1"/>
-    <row r="381" ht="17.25" customHeight="1"/>
-    <row r="382" ht="17.25" customHeight="1"/>
-    <row r="383" ht="17.25" customHeight="1"/>
-    <row r="384" ht="17.25" customHeight="1"/>
-    <row r="385" ht="17.25" customHeight="1"/>
-    <row r="386" ht="17.25" customHeight="1"/>
-    <row r="387" ht="17.25" customHeight="1"/>
-    <row r="388" ht="17.25" customHeight="1"/>
-    <row r="389" ht="17.25" customHeight="1"/>
-    <row r="390" ht="17.25" customHeight="1"/>
-    <row r="391" ht="17.25" customHeight="1"/>
-    <row r="392" ht="17.25" customHeight="1"/>
-    <row r="393" ht="17.25" customHeight="1"/>
-    <row r="394" ht="17.25" customHeight="1"/>
-    <row r="395" ht="17.25" customHeight="1"/>
-    <row r="396" ht="17.25" customHeight="1"/>
-    <row r="397" ht="17.25" customHeight="1"/>
-    <row r="398" ht="17.25" customHeight="1"/>
-    <row r="399" ht="17.25" customHeight="1"/>
-    <row r="400" ht="17.25" customHeight="1"/>
-    <row r="401" ht="17.25" customHeight="1"/>
-    <row r="402" ht="17.25" customHeight="1"/>
-    <row r="403" ht="17.25" customHeight="1"/>
-    <row r="404" ht="17.25" customHeight="1"/>
-    <row r="405" ht="17.25" customHeight="1"/>
-    <row r="406" ht="17.25" customHeight="1"/>
-    <row r="407" ht="17.25" customHeight="1"/>
-    <row r="408" ht="17.25" customHeight="1"/>
-    <row r="409" ht="17.25" customHeight="1"/>
-    <row r="410" ht="17.25" customHeight="1"/>
-    <row r="411" ht="17.25" customHeight="1"/>
-    <row r="412" ht="17.25" customHeight="1"/>
-    <row r="413" ht="17.25" customHeight="1"/>
-    <row r="414" ht="17.25" customHeight="1"/>
-    <row r="415" ht="17.25" customHeight="1"/>
-    <row r="416" ht="17.25" customHeight="1"/>
-    <row r="417" ht="17.25" customHeight="1"/>
-    <row r="418" ht="17.25" customHeight="1"/>
-    <row r="419" ht="17.25" customHeight="1"/>
-    <row r="420" ht="17.25" customHeight="1"/>
-    <row r="421" ht="17.25" customHeight="1"/>
-    <row r="422" ht="17.25" customHeight="1"/>
-    <row r="423" ht="17.25" customHeight="1"/>
-    <row r="424" ht="17.25" customHeight="1"/>
-    <row r="425" ht="17.25" customHeight="1"/>
-    <row r="426" ht="17.25" customHeight="1"/>
-    <row r="427" ht="17.25" customHeight="1"/>
-    <row r="428" ht="17.25" customHeight="1"/>
-    <row r="429" ht="17.25" customHeight="1"/>
-    <row r="430" ht="17.25" customHeight="1"/>
-    <row r="431" ht="17.25" customHeight="1"/>
-    <row r="432" ht="17.25" customHeight="1"/>
-    <row r="433" ht="17.25" customHeight="1"/>
-    <row r="434" ht="17.25" customHeight="1"/>
-    <row r="435" ht="17.25" customHeight="1"/>
-    <row r="436" ht="17.25" customHeight="1"/>
-    <row r="437" ht="17.25" customHeight="1"/>
-    <row r="438" ht="17.25" customHeight="1"/>
-    <row r="439" ht="17.25" customHeight="1"/>
-    <row r="440" ht="17.25" customHeight="1"/>
-    <row r="441" ht="17.25" customHeight="1"/>
-    <row r="442" ht="17.25" customHeight="1"/>
-    <row r="443" ht="17.25" customHeight="1"/>
-    <row r="444" ht="17.25" customHeight="1"/>
-    <row r="445" ht="17.25" customHeight="1"/>
-    <row r="446" ht="17.25" customHeight="1"/>
-    <row r="447" ht="17.25" customHeight="1"/>
-    <row r="448" ht="17.25" customHeight="1"/>
-    <row r="449" ht="17.25" customHeight="1"/>
-    <row r="450" ht="17.25" customHeight="1"/>
-    <row r="451" ht="17.25" customHeight="1"/>
-    <row r="452" ht="17.25" customHeight="1"/>
-    <row r="453" ht="17.25" customHeight="1"/>
-    <row r="454" ht="17.25" customHeight="1"/>
-    <row r="455" ht="17.25" customHeight="1"/>
-    <row r="456" ht="17.25" customHeight="1"/>
-    <row r="457" ht="17.25" customHeight="1"/>
-    <row r="458" ht="17.25" customHeight="1"/>
-    <row r="459" ht="17.25" customHeight="1"/>
-    <row r="460" ht="17.25" customHeight="1"/>
-    <row r="461" ht="17.25" customHeight="1"/>
-    <row r="462" ht="17.25" customHeight="1"/>
-    <row r="463" ht="17.25" customHeight="1"/>
-    <row r="464" ht="17.25" customHeight="1"/>
-    <row r="465" ht="17.25" customHeight="1"/>
-    <row r="466" ht="17.25" customHeight="1"/>
-    <row r="467" ht="17.25" customHeight="1"/>
-    <row r="468" ht="17.25" customHeight="1"/>
-    <row r="469" ht="17.25" customHeight="1"/>
-    <row r="470" ht="17.25" customHeight="1"/>
-    <row r="471" ht="17.25" customHeight="1"/>
-    <row r="472" ht="17.25" customHeight="1"/>
-    <row r="473" ht="17.25" customHeight="1"/>
-    <row r="474" ht="17.25" customHeight="1"/>
-    <row r="475" ht="17.25" customHeight="1"/>
-    <row r="476" ht="17.25" customHeight="1"/>
-    <row r="477" ht="17.25" customHeight="1"/>
-    <row r="478" ht="17.25" customHeight="1"/>
-    <row r="479" ht="17.25" customHeight="1"/>
-    <row r="480" ht="17.25" customHeight="1"/>
-    <row r="481" ht="17.25" customHeight="1"/>
-    <row r="482" ht="17.25" customHeight="1"/>
-    <row r="483" ht="17.25" customHeight="1"/>
-    <row r="484" ht="17.25" customHeight="1"/>
-    <row r="485" ht="17.25" customHeight="1"/>
-    <row r="486" ht="17.25" customHeight="1"/>
-    <row r="487" ht="17.25" customHeight="1"/>
-    <row r="488" ht="17.25" customHeight="1"/>
-    <row r="489" ht="17.25" customHeight="1"/>
-    <row r="490" ht="17.25" customHeight="1"/>
-    <row r="491" ht="17.25" customHeight="1"/>
-    <row r="492" ht="17.25" customHeight="1"/>
-    <row r="493" ht="17.25" customHeight="1"/>
-    <row r="494" ht="17.25" customHeight="1"/>
-    <row r="495" ht="17.25" customHeight="1"/>
-    <row r="496" ht="17.25" customHeight="1"/>
-    <row r="497" ht="17.25" customHeight="1"/>
-    <row r="498" ht="17.25" customHeight="1"/>
-    <row r="499" ht="17.25" customHeight="1"/>
-    <row r="500" ht="17.25" customHeight="1"/>
-    <row r="501" ht="17.25" customHeight="1"/>
-    <row r="502" ht="17.25" customHeight="1"/>
-    <row r="503" ht="17.25" customHeight="1"/>
-    <row r="504" ht="17.25" customHeight="1"/>
-    <row r="505" ht="17.25" customHeight="1"/>
-    <row r="506" ht="17.25" customHeight="1"/>
-    <row r="507" ht="17.25" customHeight="1"/>
-    <row r="508" ht="17.25" customHeight="1"/>
-    <row r="509" ht="17.25" customHeight="1"/>
-    <row r="510" ht="17.25" customHeight="1"/>
-    <row r="511" ht="17.25" customHeight="1"/>
-    <row r="512" ht="17.25" customHeight="1"/>
-    <row r="513" ht="17.25" customHeight="1"/>
-    <row r="514" ht="17.25" customHeight="1"/>
-    <row r="515" ht="17.25" customHeight="1"/>
-    <row r="516" ht="17.25" customHeight="1"/>
-    <row r="517" ht="17.25" customHeight="1"/>
-    <row r="518" ht="17.25" customHeight="1"/>
-    <row r="519" ht="17.25" customHeight="1"/>
-    <row r="520" ht="17.25" customHeight="1"/>
-    <row r="521" ht="17.25" customHeight="1"/>
-    <row r="522" ht="17.25" customHeight="1"/>
-    <row r="523" ht="17.25" customHeight="1"/>
-    <row r="524" ht="17.25" customHeight="1"/>
-    <row r="525" ht="17.25" customHeight="1"/>
-    <row r="526" ht="17.25" customHeight="1"/>
-    <row r="527" ht="17.25" customHeight="1"/>
-    <row r="528" ht="17.25" customHeight="1"/>
-    <row r="529" ht="17.25" customHeight="1"/>
-    <row r="530" ht="17.25" customHeight="1"/>
-    <row r="531" ht="17.25" customHeight="1"/>
-    <row r="532" ht="17.25" customHeight="1"/>
-    <row r="533" ht="17.25" customHeight="1"/>
-    <row r="534" ht="17.25" customHeight="1"/>
-    <row r="535" ht="17.25" customHeight="1"/>
-    <row r="536" ht="17.25" customHeight="1"/>
-    <row r="537" ht="17.25" customHeight="1"/>
-    <row r="538" ht="17.25" customHeight="1"/>
-    <row r="539" ht="17.25" customHeight="1"/>
-    <row r="540" ht="17.25" customHeight="1"/>
-    <row r="541" ht="17.25" customHeight="1"/>
-    <row r="542" ht="17.25" customHeight="1"/>
-    <row r="543" ht="17.25" customHeight="1"/>
-    <row r="544" ht="17.25" customHeight="1"/>
-    <row r="545" ht="17.25" customHeight="1"/>
-    <row r="546" ht="17.25" customHeight="1"/>
-    <row r="547" ht="17.25" customHeight="1"/>
-    <row r="548" ht="17.25" customHeight="1"/>
-    <row r="549" ht="17.25" customHeight="1"/>
-    <row r="550" ht="17.25" customHeight="1"/>
-    <row r="551" ht="17.25" customHeight="1"/>
-    <row r="552" ht="17.25" customHeight="1"/>
-    <row r="553" ht="17.25" customHeight="1"/>
-    <row r="554" ht="17.25" customHeight="1"/>
-    <row r="555" ht="17.25" customHeight="1"/>
-    <row r="556" ht="17.25" customHeight="1"/>
-    <row r="557" ht="17.25" customHeight="1"/>
-    <row r="558" ht="17.25" customHeight="1"/>
-    <row r="559" ht="17.25" customHeight="1"/>
-    <row r="560" ht="17.25" customHeight="1"/>
-    <row r="561" ht="17.25" customHeight="1"/>
-    <row r="562" ht="17.25" customHeight="1"/>
-    <row r="563" ht="17.25" customHeight="1"/>
-    <row r="564" ht="17.25" customHeight="1"/>
-    <row r="565" ht="17.25" customHeight="1"/>
-    <row r="566" ht="17.25" customHeight="1"/>
-    <row r="567" ht="17.25" customHeight="1"/>
-    <row r="568" ht="17.25" customHeight="1"/>
-    <row r="569" ht="17.25" customHeight="1"/>
-    <row r="570" ht="17.25" customHeight="1"/>
-    <row r="571" ht="17.25" customHeight="1"/>
-    <row r="572" ht="17.25" customHeight="1"/>
-    <row r="573" ht="17.25" customHeight="1"/>
-    <row r="574" ht="17.25" customHeight="1"/>
-    <row r="575" ht="17.25" customHeight="1"/>
-    <row r="576" ht="17.25" customHeight="1"/>
-    <row r="577" ht="17.25" customHeight="1"/>
-    <row r="578" ht="17.25" customHeight="1"/>
-    <row r="579" ht="17.25" customHeight="1"/>
-    <row r="580" ht="17.25" customHeight="1"/>
-    <row r="581" ht="17.25" customHeight="1"/>
-    <row r="582" ht="17.25" customHeight="1"/>
-    <row r="583" ht="17.25" customHeight="1"/>
-    <row r="584" ht="17.25" customHeight="1"/>
-    <row r="585" ht="17.25" customHeight="1"/>
-    <row r="586" ht="17.25" customHeight="1"/>
-    <row r="587" ht="17.25" customHeight="1"/>
-    <row r="588" ht="17.25" customHeight="1"/>
-    <row r="589" ht="17.25" customHeight="1"/>
-    <row r="590" ht="17.25" customHeight="1"/>
-    <row r="591" ht="17.25" customHeight="1"/>
-    <row r="592" ht="17.25" customHeight="1"/>
-    <row r="593" ht="17.25" customHeight="1"/>
-    <row r="594" ht="17.25" customHeight="1"/>
-    <row r="595" ht="17.25" customHeight="1"/>
-    <row r="596" ht="17.25" customHeight="1"/>
-    <row r="597" ht="17.25" customHeight="1"/>
-    <row r="598" ht="17.25" customHeight="1"/>
-    <row r="599" ht="17.25" customHeight="1"/>
-    <row r="600" ht="17.25" customHeight="1"/>
-    <row r="601" ht="17.25" customHeight="1"/>
-    <row r="602" ht="17.25" customHeight="1"/>
-    <row r="603" ht="17.25" customHeight="1"/>
-    <row r="604" ht="17.25" customHeight="1"/>
-    <row r="605" ht="17.25" customHeight="1"/>
-    <row r="606" ht="17.25" customHeight="1"/>
-    <row r="607" ht="17.25" customHeight="1"/>
-    <row r="608" ht="17.25" customHeight="1"/>
-    <row r="609" ht="17.25" customHeight="1"/>
-    <row r="610" ht="17.25" customHeight="1"/>
-    <row r="611" ht="17.25" customHeight="1"/>
-    <row r="612" ht="17.25" customHeight="1"/>
-    <row r="613" ht="17.25" customHeight="1"/>
-    <row r="614" ht="17.25" customHeight="1"/>
-    <row r="615" ht="17.25" customHeight="1"/>
-    <row r="616" ht="17.25" customHeight="1"/>
-    <row r="617" ht="17.25" customHeight="1"/>
-    <row r="618" ht="17.25" customHeight="1"/>
-    <row r="619" ht="17.25" customHeight="1"/>
-    <row r="620" ht="17.25" customHeight="1"/>
-    <row r="621" ht="17.25" customHeight="1"/>
-    <row r="622" ht="17.25" customHeight="1"/>
-    <row r="623" ht="17.25" customHeight="1"/>
-    <row r="624" ht="17.25" customHeight="1"/>
-    <row r="625" ht="17.25" customHeight="1"/>
-    <row r="626" ht="17.25" customHeight="1"/>
-    <row r="627" ht="17.25" customHeight="1"/>
-    <row r="628" ht="17.25" customHeight="1"/>
-    <row r="629" ht="17.25" customHeight="1"/>
-    <row r="630" ht="17.25" customHeight="1"/>
-    <row r="631" ht="17.25" customHeight="1"/>
-    <row r="632" ht="17.25" customHeight="1"/>
-    <row r="633" ht="17.25" customHeight="1"/>
-    <row r="634" ht="17.25" customHeight="1"/>
-    <row r="635" ht="17.25" customHeight="1"/>
-    <row r="636" ht="17.25" customHeight="1"/>
-    <row r="637" ht="17.25" customHeight="1"/>
-    <row r="638" ht="17.25" customHeight="1"/>
-    <row r="639" ht="17.25" customHeight="1"/>
-    <row r="640" ht="17.25" customHeight="1"/>
-    <row r="641" ht="17.25" customHeight="1"/>
-    <row r="642" ht="17.25" customHeight="1"/>
-    <row r="643" ht="17.25" customHeight="1"/>
-    <row r="644" ht="17.25" customHeight="1"/>
-    <row r="645" ht="17.25" customHeight="1"/>
-    <row r="646" ht="17.25" customHeight="1"/>
-    <row r="647" ht="17.25" customHeight="1"/>
-    <row r="648" ht="17.25" customHeight="1"/>
-    <row r="649" ht="17.25" customHeight="1"/>
-    <row r="650" ht="17.25" customHeight="1"/>
-    <row r="651" ht="17.25" customHeight="1"/>
-    <row r="652" ht="17.25" customHeight="1"/>
-    <row r="653" ht="17.25" customHeight="1"/>
-    <row r="654" ht="17.25" customHeight="1"/>
-    <row r="655" ht="17.25" customHeight="1"/>
-    <row r="656" ht="17.25" customHeight="1"/>
-    <row r="657" ht="17.25" customHeight="1"/>
-    <row r="658" ht="17.25" customHeight="1"/>
-    <row r="659" ht="17.25" customHeight="1"/>
-    <row r="660" ht="17.25" customHeight="1"/>
-    <row r="661" ht="17.25" customHeight="1"/>
-    <row r="662" ht="17.25" customHeight="1"/>
-    <row r="663" ht="17.25" customHeight="1"/>
-    <row r="664" ht="17.25" customHeight="1"/>
-    <row r="665" ht="17.25" customHeight="1"/>
-    <row r="666" ht="17.25" customHeight="1"/>
-    <row r="667" ht="17.25" customHeight="1"/>
-    <row r="668" ht="17.25" customHeight="1"/>
-    <row r="669" ht="17.25" customHeight="1"/>
-    <row r="670" ht="17.25" customHeight="1"/>
-    <row r="671" ht="17.25" customHeight="1"/>
-    <row r="672" ht="17.25" customHeight="1"/>
-    <row r="673" ht="17.25" customHeight="1"/>
-    <row r="674" ht="17.25" customHeight="1"/>
-    <row r="675" ht="17.25" customHeight="1"/>
-    <row r="676" ht="17.25" customHeight="1"/>
-    <row r="677" ht="17.25" customHeight="1"/>
-    <row r="678" ht="17.25" customHeight="1"/>
-    <row r="679" ht="17.25" customHeight="1"/>
-    <row r="680" ht="17.25" customHeight="1"/>
-    <row r="681" ht="17.25" customHeight="1"/>
-    <row r="682" ht="17.25" customHeight="1"/>
-    <row r="683" ht="17.25" customHeight="1"/>
-    <row r="684" ht="17.25" customHeight="1"/>
-    <row r="685" ht="17.25" customHeight="1"/>
-    <row r="686" ht="17.25" customHeight="1"/>
-    <row r="687" ht="17.25" customHeight="1"/>
-    <row r="688" ht="17.25" customHeight="1"/>
-    <row r="689" ht="17.25" customHeight="1"/>
-    <row r="690" ht="17.25" customHeight="1"/>
-    <row r="691" ht="17.25" customHeight="1"/>
-    <row r="692" ht="17.25" customHeight="1"/>
-    <row r="693" ht="17.25" customHeight="1"/>
-    <row r="694" ht="17.25" customHeight="1"/>
-    <row r="695" ht="17.25" customHeight="1"/>
-    <row r="696" ht="17.25" customHeight="1"/>
-    <row r="697" ht="17.25" customHeight="1"/>
-    <row r="698" ht="17.25" customHeight="1"/>
-    <row r="699" ht="17.25" customHeight="1"/>
-    <row r="700" ht="17.25" customHeight="1"/>
-    <row r="701" ht="17.25" customHeight="1"/>
-    <row r="702" ht="17.25" customHeight="1"/>
-    <row r="703" ht="17.25" customHeight="1"/>
-    <row r="704" ht="17.25" customHeight="1"/>
-    <row r="705" ht="17.25" customHeight="1"/>
-    <row r="706" ht="17.25" customHeight="1"/>
-    <row r="707" ht="17.25" customHeight="1"/>
-    <row r="708" ht="17.25" customHeight="1"/>
-    <row r="709" ht="17.25" customHeight="1"/>
-    <row r="710" ht="17.25" customHeight="1"/>
-    <row r="711" ht="17.25" customHeight="1"/>
-    <row r="712" ht="17.25" customHeight="1"/>
-    <row r="713" ht="17.25" customHeight="1"/>
-    <row r="714" ht="17.25" customHeight="1"/>
-    <row r="715" ht="17.25" customHeight="1"/>
-    <row r="716" ht="17.25" customHeight="1"/>
-    <row r="717" ht="17.25" customHeight="1"/>
-    <row r="718" ht="17.25" customHeight="1"/>
-    <row r="719" ht="17.25" customHeight="1"/>
-    <row r="720" ht="17.25" customHeight="1"/>
-    <row r="721" ht="17.25" customHeight="1"/>
-    <row r="722" ht="17.25" customHeight="1"/>
-    <row r="723" ht="17.25" customHeight="1"/>
-    <row r="724" ht="17.25" customHeight="1"/>
-    <row r="725" ht="17.25" customHeight="1"/>
-    <row r="726" ht="17.25" customHeight="1"/>
-    <row r="727" ht="17.25" customHeight="1"/>
-    <row r="728" ht="17.25" customHeight="1"/>
-    <row r="729" ht="17.25" customHeight="1"/>
-    <row r="730" ht="17.25" customHeight="1"/>
-    <row r="731" ht="17.25" customHeight="1"/>
-    <row r="732" ht="17.25" customHeight="1"/>
-    <row r="733" ht="17.25" customHeight="1"/>
-    <row r="734" ht="17.25" customHeight="1"/>
-    <row r="735" ht="17.25" customHeight="1"/>
-    <row r="736" ht="17.25" customHeight="1"/>
-    <row r="737" ht="17.25" customHeight="1"/>
-    <row r="738" ht="17.25" customHeight="1"/>
-    <row r="739" ht="17.25" customHeight="1"/>
-    <row r="740" ht="17.25" customHeight="1"/>
-    <row r="741" ht="17.25" customHeight="1"/>
-    <row r="742" ht="17.25" customHeight="1"/>
-    <row r="743" ht="17.25" customHeight="1"/>
-    <row r="744" ht="17.25" customHeight="1"/>
-    <row r="745" ht="17.25" customHeight="1"/>
-    <row r="746" ht="17.25" customHeight="1"/>
-    <row r="747" ht="17.25" customHeight="1"/>
-    <row r="748" ht="17.25" customHeight="1"/>
-    <row r="749" ht="17.25" customHeight="1"/>
-    <row r="750" ht="17.25" customHeight="1"/>
-    <row r="751" ht="17.25" customHeight="1"/>
-    <row r="752" ht="17.25" customHeight="1"/>
-    <row r="753" ht="17.25" customHeight="1"/>
-    <row r="754" ht="17.25" customHeight="1"/>
-    <row r="755" ht="17.25" customHeight="1"/>
-    <row r="756" ht="17.25" customHeight="1"/>
-    <row r="757" ht="17.25" customHeight="1"/>
-    <row r="758" ht="17.25" customHeight="1"/>
-    <row r="759" ht="17.25" customHeight="1"/>
-    <row r="760" ht="17.25" customHeight="1"/>
-    <row r="761" ht="17.25" customHeight="1"/>
-    <row r="762" ht="17.25" customHeight="1"/>
-    <row r="763" ht="17.25" customHeight="1"/>
-    <row r="764" ht="17.25" customHeight="1"/>
-    <row r="765" ht="17.25" customHeight="1"/>
-    <row r="766" ht="17.25" customHeight="1"/>
-    <row r="767" ht="17.25" customHeight="1"/>
-    <row r="768" ht="17.25" customHeight="1"/>
-    <row r="769" ht="17.25" customHeight="1"/>
-    <row r="770" ht="17.25" customHeight="1"/>
-    <row r="771" ht="17.25" customHeight="1"/>
-    <row r="772" ht="17.25" customHeight="1"/>
-    <row r="773" ht="17.25" customHeight="1"/>
-    <row r="774" ht="17.25" customHeight="1"/>
-    <row r="775" ht="17.25" customHeight="1"/>
-    <row r="776" ht="17.25" customHeight="1"/>
-    <row r="777" ht="17.25" customHeight="1"/>
-    <row r="778" ht="17.25" customHeight="1"/>
-    <row r="779" ht="17.25" customHeight="1"/>
-    <row r="780" ht="17.25" customHeight="1"/>
-    <row r="781" ht="17.25" customHeight="1"/>
-    <row r="782" ht="17.25" customHeight="1"/>
-    <row r="783" ht="17.25" customHeight="1"/>
-    <row r="784" ht="17.25" customHeight="1"/>
-    <row r="785" ht="17.25" customHeight="1"/>
-    <row r="786" ht="17.25" customHeight="1"/>
-    <row r="787" ht="17.25" customHeight="1"/>
-    <row r="788" ht="17.25" customHeight="1"/>
-    <row r="789" ht="17.25" customHeight="1"/>
-    <row r="790" ht="17.25" customHeight="1"/>
-    <row r="791" ht="17.25" customHeight="1"/>
-    <row r="792" ht="17.25" customHeight="1"/>
-    <row r="793" ht="17.25" customHeight="1"/>
-    <row r="794" ht="17.25" customHeight="1"/>
-    <row r="795" ht="17.25" customHeight="1"/>
-    <row r="796" ht="17.25" customHeight="1"/>
-    <row r="797" ht="17.25" customHeight="1"/>
-    <row r="798" ht="17.25" customHeight="1"/>
-    <row r="799" ht="17.25" customHeight="1"/>
-    <row r="800" ht="17.25" customHeight="1"/>
-    <row r="801" ht="17.25" customHeight="1"/>
-    <row r="802" ht="17.25" customHeight="1"/>
-    <row r="803" ht="17.25" customHeight="1"/>
-    <row r="804" ht="17.25" customHeight="1"/>
-    <row r="805" ht="17.25" customHeight="1"/>
-    <row r="806" ht="17.25" customHeight="1"/>
-    <row r="807" ht="17.25" customHeight="1"/>
-    <row r="808" ht="17.25" customHeight="1"/>
-    <row r="809" ht="17.25" customHeight="1"/>
-    <row r="810" ht="17.25" customHeight="1"/>
-    <row r="811" ht="17.25" customHeight="1"/>
-    <row r="812" ht="17.25" customHeight="1"/>
-    <row r="813" ht="17.25" customHeight="1"/>
-    <row r="814" ht="17.25" customHeight="1"/>
-    <row r="815" ht="17.25" customHeight="1"/>
-    <row r="816" ht="17.25" customHeight="1"/>
-    <row r="817" ht="17.25" customHeight="1"/>
-    <row r="818" ht="17.25" customHeight="1"/>
-    <row r="819" ht="17.25" customHeight="1"/>
-    <row r="820" ht="17.25" customHeight="1"/>
-    <row r="821" ht="17.25" customHeight="1"/>
-    <row r="822" ht="17.25" customHeight="1"/>
-    <row r="823" ht="17.25" customHeight="1"/>
-    <row r="824" ht="17.25" customHeight="1"/>
-    <row r="825" ht="17.25" customHeight="1"/>
-    <row r="826" ht="17.25" customHeight="1"/>
-    <row r="827" ht="17.25" customHeight="1"/>
-    <row r="828" ht="17.25" customHeight="1"/>
-    <row r="829" ht="17.25" customHeight="1"/>
-    <row r="830" ht="17.25" customHeight="1"/>
-    <row r="831" ht="17.25" customHeight="1"/>
-    <row r="832" ht="17.25" customHeight="1"/>
-    <row r="833" ht="17.25" customHeight="1"/>
-    <row r="834" ht="17.25" customHeight="1"/>
-    <row r="835" ht="17.25" customHeight="1"/>
-    <row r="836" ht="17.25" customHeight="1"/>
-    <row r="837" ht="17.25" customHeight="1"/>
-    <row r="838" ht="17.25" customHeight="1"/>
-    <row r="839" ht="17.25" customHeight="1"/>
-    <row r="840" ht="17.25" customHeight="1"/>
-    <row r="841" ht="17.25" customHeight="1"/>
-    <row r="842" ht="17.25" customHeight="1"/>
-    <row r="843" ht="17.25" customHeight="1"/>
-    <row r="844" ht="17.25" customHeight="1"/>
-    <row r="845" ht="17.25" customHeight="1"/>
-    <row r="846" ht="17.25" customHeight="1"/>
-    <row r="847" ht="17.25" customHeight="1"/>
-    <row r="848" ht="17.25" customHeight="1"/>
-    <row r="849" ht="17.25" customHeight="1"/>
-    <row r="850" ht="17.25" customHeight="1"/>
-    <row r="851" ht="17.25" customHeight="1"/>
-    <row r="852" ht="17.25" customHeight="1"/>
-    <row r="853" ht="17.25" customHeight="1"/>
-    <row r="854" ht="17.25" customHeight="1"/>
-    <row r="855" ht="17.25" customHeight="1"/>
-    <row r="856" ht="17.25" customHeight="1"/>
-    <row r="857" ht="17.25" customHeight="1"/>
-    <row r="858" ht="17.25" customHeight="1"/>
-    <row r="859" ht="17.25" customHeight="1"/>
-    <row r="860" ht="17.25" customHeight="1"/>
-    <row r="861" ht="17.25" customHeight="1"/>
-    <row r="862" ht="17.25" customHeight="1"/>
-    <row r="863" ht="17.25" customHeight="1"/>
-    <row r="864" ht="17.25" customHeight="1"/>
-    <row r="865" ht="17.25" customHeight="1"/>
-    <row r="866" ht="17.25" customHeight="1"/>
-    <row r="867" ht="17.25" customHeight="1"/>
-    <row r="868" ht="17.25" customHeight="1"/>
-    <row r="869" ht="17.25" customHeight="1"/>
-    <row r="870" ht="17.25" customHeight="1"/>
-    <row r="871" ht="17.25" customHeight="1"/>
-    <row r="872" ht="17.25" customHeight="1"/>
-    <row r="873" ht="17.25" customHeight="1"/>
-    <row r="874" ht="17.25" customHeight="1"/>
-    <row r="875" ht="17.25" customHeight="1"/>
-    <row r="876" ht="17.25" customHeight="1"/>
-    <row r="877" ht="17.25" customHeight="1"/>
-    <row r="878" ht="17.25" customHeight="1"/>
-    <row r="879" ht="17.25" customHeight="1"/>
-    <row r="880" ht="17.25" customHeight="1"/>
-    <row r="881" ht="17.25" customHeight="1"/>
-    <row r="882" ht="17.25" customHeight="1"/>
-    <row r="883" ht="17.25" customHeight="1"/>
-    <row r="884" ht="17.25" customHeight="1"/>
-    <row r="885" ht="17.25" customHeight="1"/>
-    <row r="886" ht="17.25" customHeight="1"/>
-    <row r="887" ht="17.25" customHeight="1"/>
-    <row r="888" ht="17.25" customHeight="1"/>
-    <row r="889" ht="17.25" customHeight="1"/>
-    <row r="890" ht="17.25" customHeight="1"/>
-    <row r="891" ht="17.25" customHeight="1"/>
-    <row r="892" ht="17.25" customHeight="1"/>
-    <row r="893" ht="17.25" customHeight="1"/>
-    <row r="894" ht="17.25" customHeight="1"/>
-    <row r="895" ht="17.25" customHeight="1"/>
-    <row r="896" ht="17.25" customHeight="1"/>
-    <row r="897" ht="17.25" customHeight="1"/>
-    <row r="898" ht="17.25" customHeight="1"/>
-    <row r="899" ht="17.25" customHeight="1"/>
-    <row r="900" ht="17.25" customHeight="1"/>
-    <row r="901" ht="17.25" customHeight="1"/>
-    <row r="902" ht="17.25" customHeight="1"/>
-    <row r="903" ht="17.25" customHeight="1"/>
-    <row r="904" ht="17.25" customHeight="1"/>
-    <row r="905" ht="17.25" customHeight="1"/>
-    <row r="906" ht="17.25" customHeight="1"/>
-    <row r="907" ht="17.25" customHeight="1"/>
-    <row r="908" ht="17.25" customHeight="1"/>
-    <row r="909" ht="17.25" customHeight="1"/>
-    <row r="910" ht="17.25" customHeight="1"/>
-    <row r="911" ht="17.25" customHeight="1"/>
-    <row r="912" ht="17.25" customHeight="1"/>
-    <row r="913" ht="17.25" customHeight="1"/>
-    <row r="914" ht="17.25" customHeight="1"/>
-    <row r="915" ht="17.25" customHeight="1"/>
-    <row r="916" ht="17.25" customHeight="1"/>
-    <row r="917" ht="17.25" customHeight="1"/>
-    <row r="918" ht="17.25" customHeight="1"/>
-    <row r="919" ht="17.25" customHeight="1"/>
-    <row r="920" ht="17.25" customHeight="1"/>
-    <row r="921" ht="17.25" customHeight="1"/>
-    <row r="922" ht="17.25" customHeight="1"/>
-    <row r="923" ht="17.25" customHeight="1"/>
-    <row r="924" ht="17.25" customHeight="1"/>
-    <row r="925" ht="17.25" customHeight="1"/>
-    <row r="926" ht="17.25" customHeight="1"/>
-    <row r="927" ht="17.25" customHeight="1"/>
-    <row r="928" ht="17.25" customHeight="1"/>
-    <row r="929" ht="17.25" customHeight="1"/>
-    <row r="930" ht="17.25" customHeight="1"/>
-    <row r="931" ht="17.25" customHeight="1"/>
-    <row r="932" ht="17.25" customHeight="1"/>
-    <row r="933" ht="17.25" customHeight="1"/>
-    <row r="934" ht="17.25" customHeight="1"/>
-    <row r="935" ht="17.25" customHeight="1"/>
-    <row r="936" ht="17.25" customHeight="1"/>
-    <row r="937" ht="17.25" customHeight="1"/>
-    <row r="938" ht="17.25" customHeight="1"/>
-    <row r="939" ht="17.25" customHeight="1"/>
-    <row r="940" ht="17.25" customHeight="1"/>
-    <row r="941" ht="17.25" customHeight="1"/>
-    <row r="942" ht="17.25" customHeight="1"/>
-    <row r="943" ht="17.25" customHeight="1"/>
-    <row r="944" ht="17.25" customHeight="1"/>
-    <row r="945" ht="17.25" customHeight="1"/>
-    <row r="946" ht="17.25" customHeight="1"/>
-    <row r="947" ht="17.25" customHeight="1"/>
-    <row r="948" ht="17.25" customHeight="1"/>
-    <row r="949" ht="17.25" customHeight="1"/>
-    <row r="950" ht="17.25" customHeight="1"/>
-    <row r="951" ht="17.25" customHeight="1"/>
-    <row r="952" ht="17.25" customHeight="1"/>
-    <row r="953" ht="17.25" customHeight="1"/>
-    <row r="954" ht="17.25" customHeight="1"/>
-    <row r="955" ht="17.25" customHeight="1"/>
-    <row r="956" ht="17.25" customHeight="1"/>
-    <row r="957" ht="17.25" customHeight="1"/>
-    <row r="958" ht="17.25" customHeight="1"/>
-    <row r="959" ht="17.25" customHeight="1"/>
-    <row r="960" ht="17.25" customHeight="1"/>
-    <row r="961" ht="17.25" customHeight="1"/>
-    <row r="962" ht="17.25" customHeight="1"/>
-    <row r="963" ht="17.25" customHeight="1"/>
-    <row r="964" ht="17.25" customHeight="1"/>
-    <row r="965" ht="17.25" customHeight="1"/>
-    <row r="966" ht="17.25" customHeight="1"/>
-    <row r="967" ht="17.25" customHeight="1"/>
-    <row r="968" ht="17.25" customHeight="1"/>
-    <row r="969" ht="17.25" customHeight="1"/>
-    <row r="970" ht="17.25" customHeight="1"/>
-    <row r="971" ht="17.25" customHeight="1"/>
-    <row r="972" ht="17.25" customHeight="1"/>
-    <row r="973" ht="17.25" customHeight="1"/>
-    <row r="974" ht="17.25" customHeight="1"/>
-    <row r="975" ht="17.25" customHeight="1"/>
-    <row r="976" ht="17.25" customHeight="1"/>
-    <row r="977" ht="17.25" customHeight="1"/>
-    <row r="978" ht="17.25" customHeight="1"/>
-    <row r="979" ht="17.25" customHeight="1"/>
-    <row r="980" ht="17.25" customHeight="1"/>
-    <row r="981" ht="17.25" customHeight="1"/>
-    <row r="982" ht="17.25" customHeight="1"/>
-    <row r="983" ht="17.25" customHeight="1"/>
-    <row r="984" ht="17.25" customHeight="1"/>
-    <row r="985" ht="17.25" customHeight="1"/>
-    <row r="986" ht="17.25" customHeight="1"/>
-    <row r="987" ht="17.25" customHeight="1"/>
-    <row r="988" ht="17.25" customHeight="1"/>
-    <row r="989" ht="17.25" customHeight="1"/>
-    <row r="990" ht="17.25" customHeight="1"/>
-    <row r="991" ht="17.25" customHeight="1"/>
-    <row r="992" ht="17.25" customHeight="1"/>
-    <row r="993" ht="17.25" customHeight="1"/>
-    <row r="994" ht="17.25" customHeight="1"/>
-    <row r="995" ht="17.25" customHeight="1"/>
-    <row r="996" ht="17.25" customHeight="1"/>
-    <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
-    <row r="999" ht="17.25" customHeight="1"/>
-    <row r="1000" ht="17.25" customHeight="1"/>
-    <row r="1001" ht="17.25" customHeight="1"/>
-    <row r="1002" ht="17.25" customHeight="1"/>
-    <row r="1003" ht="17.25" customHeight="1"/>
-    <row r="1004" ht="17.25" customHeight="1"/>
-    <row r="1005" ht="17.25" customHeight="1"/>
-    <row r="1006" ht="17.25" customHeight="1"/>
-    <row r="1007" ht="17.25" customHeight="1"/>
-    <row r="1008" ht="17.25" customHeight="1"/>
-    <row r="1009" ht="17.25" customHeight="1"/>
-    <row r="1010" ht="17.25" customHeight="1"/>
-    <row r="1011" ht="17.25" customHeight="1"/>
-    <row r="1012" ht="17.25" customHeight="1"/>
-    <row r="1013" ht="17.25" customHeight="1"/>
+        <v>812</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A94:J94"/>
@@ -10652,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>1032</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -14085,7 +13652,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>1068</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>463</v>
@@ -14679,7 +14246,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>76</v>
+        <v>1048</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>463</v>
@@ -17886,7 +17453,7 @@
     </row>
     <row r="37" spans="1:1" ht="17.25" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>137</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="17.25" customHeight="1">
@@ -18315,8 +17882,8 @@
       </c>
     </row>
     <row r="123" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A123" s="5" t="s">
-        <v>219</v>
+      <c r="A123" s="36" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="17.25" customHeight="1">
@@ -18502,8 +18069,8 @@
       </c>
     </row>
     <row r="158" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A158" s="5" t="s">
-        <v>257</v>
+      <c r="A158" s="36" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="17.25" customHeight="1">
@@ -20130,7 +19697,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -20150,7 +19717,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>1032</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -20178,7 +19745,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>1065</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -20206,7 +19773,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>1066</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>16</v>
@@ -20234,7 +19801,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>1067</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>19</v>
@@ -20262,7 +19829,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>1047</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>22</v>
@@ -20290,7 +19857,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>1068</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
@@ -20318,7 +19885,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>1069</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>340</v>
@@ -20346,7 +19913,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>1070</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
@@ -20374,7 +19941,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>1071</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
@@ -20402,7 +19969,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>1072</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
@@ -20430,7 +19997,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>1028</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
@@ -20458,7 +20025,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>1073</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -20486,7 +20053,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>1074</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>40</v>
@@ -20514,7 +20081,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>1033</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>27</v>
@@ -20542,7 +20109,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>1075</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>45</v>
@@ -20598,7 +20165,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>1076</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -21098,16 +20665,16 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.5">
-      <c r="B37" s="33" t="s">
-        <v>884</v>
-      </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="35"/>
+      <c r="B37" s="40" t="s">
+        <v>882</v>
+      </c>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:10">
       <c r="B38" s="24" t="s">
@@ -21123,7 +20690,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G38" s="24" t="s">
         <v>708</v>
@@ -21149,7 +20716,7 @@
         <v>11</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G39" s="25" t="s">
         <v>8</v>
@@ -21175,7 +20742,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G40" s="25" t="s">
         <v>49</v>
@@ -21201,7 +20768,7 @@
         <v>41</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>39</v>
@@ -21210,20 +20777,20 @@
         <v>715</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="16.5">
-      <c r="B43" s="33" t="s">
-        <v>885</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="35"/>
+      <c r="B43" s="40" t="s">
+        <v>883</v>
+      </c>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="42"/>
     </row>
     <row r="44" spans="1:10">
       <c r="B44" s="24" t="s">
@@ -21239,7 +20806,7 @@
         <v>4</v>
       </c>
       <c r="F44" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G44" s="24" t="s">
         <v>708</v>
@@ -21265,16 +20832,16 @@
         <v>717</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="H45" s="25" t="s">
         <v>718</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -21291,7 +20858,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G46" s="25" t="s">
         <v>13</v>
@@ -21317,13 +20884,13 @@
         <v>338</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="I47" s="25" t="s">
         <v>723</v>
@@ -21343,7 +20910,7 @@
         <v>20</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="G48" s="25"/>
       <c r="H48" s="25" t="s">
@@ -21367,7 +20934,7 @@
         <v>30</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G49" s="25"/>
       <c r="H49" s="25" t="s">
@@ -21391,7 +20958,7 @@
         <v>32</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="G50" s="25"/>
       <c r="H50" s="25" t="s">
@@ -21415,7 +20982,7 @@
         <v>34</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G51" s="25"/>
       <c r="H51" s="25" t="s">
@@ -21440,13 +21007,13 @@
       </c>
       <c r="F52" s="25"/>
       <c r="G52" s="25" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="H52" s="25" t="s">
         <v>732</v>
       </c>
       <c r="I52" s="25" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="16.5">
@@ -21463,7 +21030,7 @@
         <v>46</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="G53" s="25"/>
       <c r="H53" s="25" t="s">
@@ -21488,7 +21055,7 @@
       </c>
       <c r="F54" s="25"/>
       <c r="G54" s="27" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="H54" s="25" t="s">
         <v>736</v>
@@ -21498,16 +21065,16 @@
       </c>
     </row>
     <row r="56" spans="2:9" ht="16.5">
-      <c r="B56" s="33" t="s">
-        <v>988</v>
-      </c>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="34"/>
-      <c r="I56" s="35"/>
+      <c r="B56" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="42"/>
     </row>
     <row r="57" spans="2:9">
       <c r="B57" s="24" t="s">
@@ -21523,7 +21090,7 @@
         <v>4</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G57" s="24" t="s">
         <v>708</v>
@@ -21549,7 +21116,7 @@
         <v>36</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G58" s="25" t="s">
         <v>35</v>
@@ -21575,7 +21142,7 @@
         <v>38</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="G59" s="25" t="s">
         <v>37</v>
@@ -21601,16 +21168,16 @@
         <v>65</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G60" s="27" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="H60" s="25" t="s">
         <v>743</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="61" spans="2:9">
@@ -21627,7 +21194,7 @@
         <v>745</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G61" s="25"/>
       <c r="H61" s="25" t="s">
@@ -21652,7 +21219,7 @@
       </c>
       <c r="F62" s="25"/>
       <c r="G62" s="27" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="H62" s="25" t="s">
         <v>58</v>
@@ -21675,14 +21242,14 @@
         <v>343</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="G63" s="25"/>
       <c r="H63" s="25" t="s">
         <v>749</v>
       </c>
       <c r="I63" s="25" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="16.5">
@@ -21699,7 +21266,7 @@
         <v>717</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G64" s="25" t="s">
         <v>717</v>
@@ -21725,7 +21292,7 @@
         <v>717</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G65" s="25" t="s">
         <v>717</v>
@@ -21734,7 +21301,7 @@
         <v>754</v>
       </c>
       <c r="I65" s="25" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="66" spans="2:9">
@@ -21751,7 +21318,7 @@
         <v>83</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G66" s="25" t="s">
         <v>82</v>
@@ -21777,7 +21344,7 @@
         <v>717</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G67" s="25" t="s">
         <v>717</v>
@@ -21790,16 +21357,16 @@
       </c>
     </row>
     <row r="69" spans="2:9" ht="16.5">
-      <c r="B69" s="33" t="s">
-        <v>992</v>
-      </c>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="35"/>
+      <c r="B69" s="40" t="s">
+        <v>988</v>
+      </c>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="42"/>
     </row>
     <row r="70" spans="2:9">
       <c r="B70" s="24" t="s">
@@ -21815,7 +21382,7 @@
         <v>4</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G70" s="24" t="s">
         <v>708</v>
@@ -21848,7 +21415,7 @@
         <v>752</v>
       </c>
       <c r="I71" s="25" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="72" spans="2:9">
@@ -21872,7 +21439,7 @@
         <v>754</v>
       </c>
       <c r="I72" s="25" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="73" spans="2:9">
@@ -21924,16 +21491,16 @@
       </c>
     </row>
     <row r="76" spans="2:9" ht="16.5">
-      <c r="B76" s="33" t="s">
-        <v>993</v>
-      </c>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
-      <c r="E76" s="34"/>
-      <c r="F76" s="34"/>
-      <c r="G76" s="34"/>
-      <c r="H76" s="34"/>
-      <c r="I76" s="35"/>
+      <c r="B76" s="40" t="s">
+        <v>989</v>
+      </c>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="42"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="24" t="s">
@@ -21949,7 +21516,7 @@
         <v>4</v>
       </c>
       <c r="F77" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G77" s="24" t="s">
         <v>708</v>
@@ -21982,7 +21549,7 @@
         <v>765</v>
       </c>
       <c r="I78" s="25" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="79" spans="2:9">
@@ -21999,7 +21566,7 @@
         <v>63</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="G79" s="25" t="s">
         <v>61</v>
@@ -22032,20 +21599,20 @@
         <v>762</v>
       </c>
       <c r="I80" s="25" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="16.5">
-      <c r="B82" s="33" t="s">
-        <v>994</v>
-      </c>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="34"/>
-      <c r="I82" s="35"/>
+      <c r="B82" s="40" t="s">
+        <v>990</v>
+      </c>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="42"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="24" t="s">
@@ -22061,7 +21628,7 @@
         <v>4</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G83" s="24" t="s">
         <v>708</v>
@@ -22091,10 +21658,10 @@
         <v>717</v>
       </c>
       <c r="H84" s="25" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="I84" s="25" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
     </row>
     <row r="85" spans="2:9">
@@ -22118,7 +21685,7 @@
         <v>499</v>
       </c>
       <c r="I85" s="25" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="86" spans="2:9">
@@ -22136,7 +21703,7 @@
       </c>
       <c r="F86" s="25"/>
       <c r="G86" s="25" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="H86" s="25" t="s">
         <v>347</v>
@@ -22166,7 +21733,7 @@
         <v>390</v>
       </c>
       <c r="I87" s="25" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="88" spans="2:9">
@@ -22242,16 +21809,16 @@
       </c>
     </row>
     <row r="92" spans="2:9" ht="16.5">
-      <c r="B92" s="33" t="s">
-        <v>926</v>
-      </c>
-      <c r="C92" s="34"/>
-      <c r="D92" s="34"/>
-      <c r="E92" s="34"/>
-      <c r="F92" s="34"/>
-      <c r="G92" s="34"/>
-      <c r="H92" s="34"/>
-      <c r="I92" s="35"/>
+      <c r="B92" s="40" t="s">
+        <v>923</v>
+      </c>
+      <c r="C92" s="41"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="41"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="41"/>
+      <c r="H92" s="41"/>
+      <c r="I92" s="42"/>
     </row>
     <row r="93" spans="2:9">
       <c r="B93" s="24" t="s">
@@ -22267,7 +21834,7 @@
         <v>4</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G93" s="24" t="s">
         <v>708</v>
@@ -22300,7 +21867,7 @@
         <v>339</v>
       </c>
       <c r="I94" s="25" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="95" spans="2:9">
@@ -22345,10 +21912,10 @@
         <v>717</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
     </row>
     <row r="97" spans="2:9">
@@ -22393,23 +21960,23 @@
         <v>717</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="I98" s="25" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="100" spans="2:9" ht="16.5">
-      <c r="B100" s="33" t="s">
-        <v>932</v>
-      </c>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="35"/>
+      <c r="B100" s="40" t="s">
+        <v>929</v>
+      </c>
+      <c r="C100" s="41"/>
+      <c r="D100" s="41"/>
+      <c r="E100" s="41"/>
+      <c r="F100" s="41"/>
+      <c r="G100" s="41"/>
+      <c r="H100" s="41"/>
+      <c r="I100" s="42"/>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="24" t="s">
@@ -22425,7 +21992,7 @@
         <v>4</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G101" s="24" t="s">
         <v>708</v>
@@ -22439,7 +22006,7 @@
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="25" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C102" s="25" t="s">
         <v>19</v>
@@ -22455,10 +22022,10 @@
         <v>717</v>
       </c>
       <c r="H102" s="25" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="I102" s="25" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="103" spans="2:9">
@@ -22479,15 +22046,15 @@
         <v>53</v>
       </c>
       <c r="H103" s="25" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="I103" s="25" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="104" spans="2:9">
       <c r="B104" s="25" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C104" s="25" t="s">
         <v>717</v>
@@ -22503,21 +22070,21 @@
         <v>717</v>
       </c>
       <c r="H104" s="25" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="I104" s="25"/>
     </row>
     <row r="106" spans="2:9" ht="16.5">
-      <c r="B106" s="33" t="s">
-        <v>938</v>
-      </c>
-      <c r="C106" s="34"/>
-      <c r="D106" s="34"/>
-      <c r="E106" s="34"/>
-      <c r="F106" s="34"/>
-      <c r="G106" s="34"/>
-      <c r="H106" s="34"/>
-      <c r="I106" s="35"/>
+      <c r="B106" s="40" t="s">
+        <v>935</v>
+      </c>
+      <c r="C106" s="41"/>
+      <c r="D106" s="41"/>
+      <c r="E106" s="41"/>
+      <c r="F106" s="41"/>
+      <c r="G106" s="41"/>
+      <c r="H106" s="41"/>
+      <c r="I106" s="42"/>
     </row>
     <row r="107" spans="2:9">
       <c r="B107" s="24" t="s">
@@ -22533,7 +22100,7 @@
         <v>4</v>
       </c>
       <c r="F107" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G107" s="24" t="s">
         <v>708</v>
@@ -22566,7 +22133,7 @@
         <v>749</v>
       </c>
       <c r="I108" s="25" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="109" spans="2:9">
@@ -22590,20 +22157,20 @@
         <v>94</v>
       </c>
       <c r="I109" s="25" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="111" spans="2:9" ht="16.5">
-      <c r="B111" s="33" t="s">
-        <v>941</v>
-      </c>
-      <c r="C111" s="34"/>
-      <c r="D111" s="34"/>
-      <c r="E111" s="34"/>
-      <c r="F111" s="34"/>
-      <c r="G111" s="34"/>
-      <c r="H111" s="34"/>
-      <c r="I111" s="35"/>
+      <c r="B111" s="40" t="s">
+        <v>938</v>
+      </c>
+      <c r="C111" s="41"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="41"/>
+      <c r="F111" s="41"/>
+      <c r="G111" s="41"/>
+      <c r="H111" s="41"/>
+      <c r="I111" s="42"/>
     </row>
     <row r="112" spans="2:9">
       <c r="B112" s="24" t="s">
@@ -22619,7 +22186,7 @@
         <v>4</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G112" s="24" t="s">
         <v>708</v>
@@ -22633,7 +22200,7 @@
     </row>
     <row r="113" spans="2:9">
       <c r="B113" s="25" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C113" s="25" t="s">
         <v>62</v>
@@ -22649,10 +22216,10 @@
         <v>717</v>
       </c>
       <c r="H113" s="25" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="I113" s="25" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="114" spans="2:9">
@@ -22676,7 +22243,7 @@
         <v>762</v>
       </c>
       <c r="I114" s="25" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="115" spans="2:9">
@@ -22690,22 +22257,22 @@
         <v>10</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F115" s="25"/>
       <c r="G115" s="25" t="s">
         <v>78</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="I115" s="25" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="116" spans="2:9">
       <c r="B116" s="25" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C116" s="25" t="s">
         <v>560</v>
@@ -22721,23 +22288,23 @@
         <v>717</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="I116" s="25" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="118" spans="2:9" ht="16.5">
-      <c r="B118" s="33" t="s">
-        <v>946</v>
-      </c>
-      <c r="C118" s="34"/>
-      <c r="D118" s="34"/>
-      <c r="E118" s="34"/>
-      <c r="F118" s="34"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="34"/>
-      <c r="I118" s="35"/>
+      <c r="B118" s="40" t="s">
+        <v>943</v>
+      </c>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
+      <c r="F118" s="41"/>
+      <c r="G118" s="41"/>
+      <c r="H118" s="41"/>
+      <c r="I118" s="42"/>
     </row>
     <row r="119" spans="2:9">
       <c r="B119" s="24" t="s">
@@ -22753,7 +22320,7 @@
         <v>4</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G119" s="24" t="s">
         <v>708</v>
@@ -22786,12 +22353,12 @@
         <v>339</v>
       </c>
       <c r="I120" s="25" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="121" spans="2:9">
       <c r="B121" s="25" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C121" s="25" t="s">
         <v>27</v>
@@ -22807,23 +22374,23 @@
         <v>86</v>
       </c>
       <c r="H121" s="25" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="I121" s="25" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="123" spans="2:9" ht="16.5">
-      <c r="B123" s="33" t="s">
-        <v>818</v>
-      </c>
-      <c r="C123" s="34"/>
-      <c r="D123" s="34"/>
-      <c r="E123" s="34"/>
-      <c r="F123" s="34"/>
-      <c r="G123" s="34"/>
-      <c r="H123" s="34"/>
-      <c r="I123" s="35"/>
+      <c r="B123" s="40" t="s">
+        <v>816</v>
+      </c>
+      <c r="C123" s="41"/>
+      <c r="D123" s="41"/>
+      <c r="E123" s="41"/>
+      <c r="F123" s="41"/>
+      <c r="G123" s="41"/>
+      <c r="H123" s="41"/>
+      <c r="I123" s="42"/>
     </row>
     <row r="124" spans="2:9">
       <c r="B124" s="24" t="s">
@@ -22839,7 +22406,7 @@
         <v>4</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G124" s="24" t="s">
         <v>708</v>
@@ -22853,10 +22420,10 @@
     </row>
     <row r="125" spans="2:9">
       <c r="B125" s="25" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D125" s="25" t="s">
         <v>717</v>
@@ -22869,18 +22436,18 @@
         <v>21</v>
       </c>
       <c r="H125" s="25" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="I125" s="25" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="126" spans="2:9">
       <c r="B126" s="25" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D126" s="25" t="s">
         <v>717</v>
@@ -22893,18 +22460,18 @@
         <v>47</v>
       </c>
       <c r="H126" s="25" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I126" s="25" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="127" spans="2:9">
       <c r="B127" s="25" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D127" s="25" t="s">
         <v>717</v>
@@ -22917,18 +22484,18 @@
         <v>66</v>
       </c>
       <c r="H127" s="25" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="I127" s="25" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="128" spans="2:9">
       <c r="B128" s="25" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D128" s="25" t="s">
         <v>717</v>
@@ -22941,23 +22508,23 @@
         <v>51</v>
       </c>
       <c r="H128" s="25" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="I128" s="25" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="130" spans="2:9" ht="16.5">
-      <c r="B130" s="33" t="s">
-        <v>955</v>
-      </c>
-      <c r="C130" s="34"/>
-      <c r="D130" s="34"/>
-      <c r="E130" s="34"/>
-      <c r="F130" s="34"/>
-      <c r="G130" s="34"/>
-      <c r="H130" s="34"/>
-      <c r="I130" s="35"/>
+      <c r="B130" s="40" t="s">
+        <v>952</v>
+      </c>
+      <c r="C130" s="41"/>
+      <c r="D130" s="41"/>
+      <c r="E130" s="41"/>
+      <c r="F130" s="41"/>
+      <c r="G130" s="41"/>
+      <c r="H130" s="41"/>
+      <c r="I130" s="42"/>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="24" t="s">
@@ -22973,7 +22540,7 @@
         <v>4</v>
       </c>
       <c r="F131" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G131" s="24" t="s">
         <v>708</v>
@@ -22987,7 +22554,7 @@
     </row>
     <row r="132" spans="2:9">
       <c r="B132" s="25" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C132" s="25" t="s">
         <v>344</v>
@@ -23006,12 +22573,12 @@
         <v>768</v>
       </c>
       <c r="I132" s="25" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="25" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C133" s="25" t="s">
         <v>27</v>
@@ -23027,18 +22594,18 @@
         <v>86</v>
       </c>
       <c r="H133" s="25" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="I133" s="25" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="25" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D134" s="25" t="s">
         <v>717</v>
@@ -23051,10 +22618,10 @@
         <v>64</v>
       </c>
       <c r="H134" s="25" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="I134" s="25" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -25258,7 +24825,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>1067</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>19</v>
@@ -25420,7 +24987,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>1072</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
@@ -25447,7 +25014,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>1028</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
@@ -25474,7 +25041,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>1073</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -25501,7 +25068,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>1074</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>40</v>
@@ -29189,7 +28756,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>1069</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>27</v>
@@ -29270,7 +28837,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>1072</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
